--- a/data/H131_20260619_10.xlsx
+++ b/data/H131_20260619_10.xlsx
@@ -598,7 +598,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>601.0</v>
+        <v>606.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -610,10 +610,10 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>601.0</v>
+        <v>606.0</v>
       </c>
       <c r="O4" s="2">
-        <v>270.0</v>
+        <v>275.0</v>
       </c>
       <c r="P4" s="2">
         <v>331.0</v>
@@ -669,7 +669,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>501.0</v>
+        <v>525.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -681,13 +681,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>501.0</v>
+        <v>525.0</v>
       </c>
       <c r="O5" s="2">
-        <v>243.0</v>
+        <v>262.0</v>
       </c>
       <c r="P5" s="2">
-        <v>257.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q5" s="2">
         <v>1.0</v>
@@ -740,7 +740,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>693.0</v>
+        <v>720.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -752,19 +752,19 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>693.0</v>
+        <v>720.0</v>
       </c>
       <c r="O6" s="2">
-        <v>336.0</v>
+        <v>362.0</v>
       </c>
       <c r="P6" s="2">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0</v>
       </c>
       <c r="R6" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S6" s="2">
         <v>0.0</v>
@@ -779,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +811,7 @@
         <v>515.0</v>
       </c>
       <c r="J7" s="2">
-        <v>373.0</v>
+        <v>377.0</v>
       </c>
       <c r="K7" s="2">
         <v>1.0</v>
@@ -823,13 +823,13 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="2">
-        <v>373.0</v>
+        <v>377.0</v>
       </c>
       <c r="O7" s="2">
-        <v>193.0</v>
+        <v>196.0</v>
       </c>
       <c r="P7" s="2">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="Q7" s="2">
         <v>0.0</v>
@@ -882,7 +882,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" s="2">
-        <v>437.0</v>
+        <v>503.0</v>
       </c>
       <c r="K8" s="2">
         <v>1.0</v>
@@ -894,13 +894,13 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="2">
-        <v>437.0</v>
+        <v>503.0</v>
       </c>
       <c r="O8" s="2">
-        <v>236.0</v>
+        <v>292.0</v>
       </c>
       <c r="P8" s="2">
-        <v>201.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0</v>
@@ -953,7 +953,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" s="2">
-        <v>428.0</v>
+        <v>436.0</v>
       </c>
       <c r="K9" s="2">
         <v>1.0</v>
@@ -965,13 +965,13 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="2">
-        <v>428.0</v>
+        <v>436.0</v>
       </c>
       <c r="O9" s="2">
-        <v>221.0</v>
+        <v>225.0</v>
       </c>
       <c r="P9" s="2">
-        <v>207.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q9" s="2">
         <v>0.0</v>
@@ -1095,7 +1095,7 @@
         <v>561.0</v>
       </c>
       <c r="J11" s="2">
-        <v>390.0</v>
+        <v>421.0</v>
       </c>
       <c r="K11" s="2">
         <v>1.0</v>
@@ -1107,13 +1107,13 @@
         <v>0.0</v>
       </c>
       <c r="N11" s="2">
-        <v>390.0</v>
+        <v>421.0</v>
       </c>
       <c r="O11" s="2">
-        <v>237.0</v>
+        <v>253.0</v>
       </c>
       <c r="P11" s="2">
-        <v>153.0</v>
+        <v>168.0</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0</v>
@@ -1166,7 +1166,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" s="2">
-        <v>744.0</v>
+        <v>752.0</v>
       </c>
       <c r="K12" s="2">
         <v>1.0</v>
@@ -1178,13 +1178,13 @@
         <v>0.0</v>
       </c>
       <c r="N12" s="2">
-        <v>744.0</v>
+        <v>752.0</v>
       </c>
       <c r="O12" s="2">
-        <v>429.0</v>
+        <v>433.0</v>
       </c>
       <c r="P12" s="2">
-        <v>315.0</v>
+        <v>319.0</v>
       </c>
       <c r="Q12" s="2">
         <v>0.0</v>
@@ -1237,7 +1237,7 @@
         <v>1245.0</v>
       </c>
       <c r="J13" s="2">
-        <v>1061.0</v>
+        <v>1126.0</v>
       </c>
       <c r="K13" s="2">
         <v>1.0</v>
@@ -1249,13 +1249,13 @@
         <v>0.0</v>
       </c>
       <c r="N13" s="2">
-        <v>1061.0</v>
+        <v>1126.0</v>
       </c>
       <c r="O13" s="2">
-        <v>565.0</v>
+        <v>602.0</v>
       </c>
       <c r="P13" s="2">
-        <v>496.0</v>
+        <v>524.0</v>
       </c>
       <c r="Q13" s="2">
         <v>0.0</v>
@@ -1379,7 +1379,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>518.0</v>
+        <v>603.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1391,13 +1391,13 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>518.0</v>
+        <v>603.0</v>
       </c>
       <c r="O15" s="2">
-        <v>252.0</v>
+        <v>299.0</v>
       </c>
       <c r="P15" s="2">
-        <v>266.0</v>
+        <v>304.0</v>
       </c>
       <c r="Q15" s="2">
         <v>0.0</v>
@@ -1450,7 +1450,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" s="2">
-        <v>530.0</v>
+        <v>561.0</v>
       </c>
       <c r="K16" s="2">
         <v>1.0</v>
@@ -1462,13 +1462,13 @@
         <v>0.0</v>
       </c>
       <c r="N16" s="2">
-        <v>530.0</v>
+        <v>561.0</v>
       </c>
       <c r="O16" s="2">
-        <v>244.0</v>
+        <v>270.0</v>
       </c>
       <c r="P16" s="2">
-        <v>286.0</v>
+        <v>291.0</v>
       </c>
       <c r="Q16" s="2">
         <v>0.0</v>
@@ -1477,10 +1477,10 @@
         <v>3.0</v>
       </c>
       <c r="S16" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="T16" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="U16" s="2">
         <v>1.0</v>
@@ -1489,7 +1489,7 @@
         <v>0.0</v>
       </c>
       <c r="W16" s="2">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="17">
@@ -1521,7 +1521,7 @@
         <v>829.0</v>
       </c>
       <c r="J17" s="2">
-        <v>582.0</v>
+        <v>653.0</v>
       </c>
       <c r="K17" s="2">
         <v>1.0</v>
@@ -1533,13 +1533,13 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <v>582.0</v>
+        <v>653.0</v>
       </c>
       <c r="O17" s="2">
-        <v>291.0</v>
+        <v>346.0</v>
       </c>
       <c r="P17" s="2">
-        <v>291.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q17" s="2">
         <v>0.0</v>
@@ -1554,13 +1554,13 @@
         <v>2.0</v>
       </c>
       <c r="U17" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V17" s="2">
         <v>0.0</v>
       </c>
       <c r="W17" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="18">
@@ -1592,7 +1592,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" s="2">
-        <v>1111.0</v>
+        <v>1126.0</v>
       </c>
       <c r="K18" s="2">
         <v>1.0</v>
@@ -1604,13 +1604,13 @@
         <v>0.0</v>
       </c>
       <c r="N18" s="2">
-        <v>1111.0</v>
+        <v>1126.0</v>
       </c>
       <c r="O18" s="2">
-        <v>584.0</v>
+        <v>598.0</v>
       </c>
       <c r="P18" s="2">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="Q18" s="2">
         <v>0.0</v>
@@ -1619,10 +1619,10 @@
         <v>25.0</v>
       </c>
       <c r="S18" s="2">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="T18" s="2">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="U18" s="2">
         <v>11.0</v>
@@ -1631,7 +1631,7 @@
         <v>2.0</v>
       </c>
       <c r="W18" s="2">
-        <v>80.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="19">
@@ -1805,7 +1805,7 @@
         <v>926.0</v>
       </c>
       <c r="J21" s="2">
-        <v>651.0</v>
+        <v>700.0</v>
       </c>
       <c r="K21" s="2">
         <v>1.0</v>
@@ -1817,13 +1817,13 @@
         <v>0.0</v>
       </c>
       <c r="N21" s="2">
-        <v>651.0</v>
+        <v>700.0</v>
       </c>
       <c r="O21" s="2">
-        <v>336.0</v>
+        <v>365.0</v>
       </c>
       <c r="P21" s="2">
-        <v>315.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q21" s="2">
         <v>0.0</v>
@@ -1832,7 +1832,7 @@
         <v>35.0</v>
       </c>
       <c r="S21" s="2">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="T21" s="2">
         <v>0.0</v>
@@ -1844,7 +1844,7 @@
         <v>0.0</v>
       </c>
       <c r="W21" s="2">
-        <v>35.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1876,7 +1876,7 @@
         <v>1003.0</v>
       </c>
       <c r="J22" s="2">
-        <v>801.0</v>
+        <v>848.0</v>
       </c>
       <c r="K22" s="2">
         <v>1.0</v>
@@ -1888,34 +1888,34 @@
         <v>0.0</v>
       </c>
       <c r="N22" s="2">
-        <v>801.0</v>
+        <v>848.0</v>
       </c>
       <c r="O22" s="2">
-        <v>450.0</v>
+        <v>472.0</v>
       </c>
       <c r="P22" s="2">
-        <v>351.0</v>
+        <v>376.0</v>
       </c>
       <c r="Q22" s="2">
         <v>0.0</v>
       </c>
       <c r="R22" s="2">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
       <c r="S22" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="T22" s="2">
         <v>0.0</v>
       </c>
       <c r="U22" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="V22" s="2">
         <v>0.0</v>
       </c>
       <c r="W22" s="2">
-        <v>35.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1947,7 +1947,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" s="2">
-        <v>257.0</v>
+        <v>361.0</v>
       </c>
       <c r="K23" s="2">
         <v>1.0</v>
@@ -1956,25 +1956,25 @@
         <v>1.0</v>
       </c>
       <c r="M23" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="2">
-        <v>255.0</v>
+        <v>361.0</v>
       </c>
       <c r="O23" s="2">
-        <v>118.0</v>
+        <v>175.0</v>
       </c>
       <c r="P23" s="2">
-        <v>139.0</v>
+        <v>186.0</v>
       </c>
       <c r="Q23" s="2">
         <v>0.0</v>
       </c>
       <c r="R23" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S23" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="T23" s="2">
         <v>0.0</v>
@@ -1986,7 +1986,7 @@
         <v>0.0</v>
       </c>
       <c r="W23" s="2">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -2018,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>750.0</v>
+        <v>759.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2030,16 +2030,16 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>750.0</v>
+        <v>759.0</v>
       </c>
       <c r="O24" s="2">
-        <v>434.0</v>
+        <v>438.0</v>
       </c>
       <c r="P24" s="2">
-        <v>301.0</v>
+        <v>305.0</v>
       </c>
       <c r="Q24" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R24" s="2">
         <v>6.0</v>
@@ -2048,7 +2048,7 @@
         <v>0.0</v>
       </c>
       <c r="T24" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U24" s="2">
         <v>1.0</v>
@@ -2057,7 +2057,7 @@
         <v>0.0</v>
       </c>
       <c r="W24" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2089,7 +2089,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" s="2">
-        <v>304.0</v>
+        <v>354.0</v>
       </c>
       <c r="K25" s="2">
         <v>1.0</v>
@@ -2101,13 +2101,13 @@
         <v>0.0</v>
       </c>
       <c r="N25" s="2">
-        <v>304.0</v>
+        <v>354.0</v>
       </c>
       <c r="O25" s="2">
-        <v>216.0</v>
+        <v>251.0</v>
       </c>
       <c r="P25" s="2">
-        <v>88.0</v>
+        <v>103.0</v>
       </c>
       <c r="Q25" s="2">
         <v>0.0</v>
@@ -2160,7 +2160,7 @@
         <v>1399.0</v>
       </c>
       <c r="J26" s="2">
-        <v>1045.0</v>
+        <v>1111.0</v>
       </c>
       <c r="K26" s="2">
         <v>1.0</v>
@@ -2172,13 +2172,13 @@
         <v>0.0</v>
       </c>
       <c r="N26" s="2">
-        <v>1045.0</v>
+        <v>1111.0</v>
       </c>
       <c r="O26" s="2">
-        <v>533.0</v>
+        <v>586.0</v>
       </c>
       <c r="P26" s="2">
-        <v>512.0</v>
+        <v>525.0</v>
       </c>
       <c r="Q26" s="2">
         <v>0.0</v>
@@ -2231,7 +2231,7 @@
         <v>820.0</v>
       </c>
       <c r="J27" s="2">
-        <v>663.0</v>
+        <v>680.0</v>
       </c>
       <c r="K27" s="2">
         <v>1.0</v>
@@ -2243,10 +2243,10 @@
         <v>0.0</v>
       </c>
       <c r="N27" s="2">
-        <v>663.0</v>
+        <v>680.0</v>
       </c>
       <c r="O27" s="2">
-        <v>340.0</v>
+        <v>357.0</v>
       </c>
       <c r="P27" s="2">
         <v>323.0</v>
@@ -2258,7 +2258,7 @@
         <v>14.0</v>
       </c>
       <c r="S27" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="T27" s="2">
         <v>0.0</v>
@@ -2270,7 +2270,7 @@
         <v>0.0</v>
       </c>
       <c r="W27" s="2">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -2302,7 +2302,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>1002.0</v>
+        <v>1014.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2314,25 +2314,25 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>1002.0</v>
+        <v>1014.0</v>
       </c>
       <c r="O28" s="2">
-        <v>545.0</v>
+        <v>555.0</v>
       </c>
       <c r="P28" s="2">
-        <v>455.0</v>
+        <v>457.0</v>
       </c>
       <c r="Q28" s="2">
         <v>2.0</v>
       </c>
       <c r="R28" s="2">
-        <v>5.0</v>
+        <v>35.0</v>
       </c>
       <c r="S28" s="2">
-        <v>2.0</v>
+        <v>27.0</v>
       </c>
       <c r="T28" s="2">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="U28" s="2">
         <v>0.0</v>
@@ -2341,7 +2341,7 @@
         <v>0.0</v>
       </c>
       <c r="W28" s="2">
-        <v>8.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -2373,7 +2373,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>400.0</v>
+        <v>422.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2385,13 +2385,13 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>400.0</v>
+        <v>422.0</v>
       </c>
       <c r="O29" s="2">
-        <v>62.0</v>
+        <v>74.0</v>
       </c>
       <c r="P29" s="2">
-        <v>206.0</v>
+        <v>216.0</v>
       </c>
       <c r="Q29" s="2">
         <v>132.0</v>
@@ -2444,7 +2444,7 @@
         <v>258.0</v>
       </c>
       <c r="J30" s="2">
-        <v>229.0</v>
+        <v>233.0</v>
       </c>
       <c r="K30" s="2">
         <v>1.0</v>
@@ -2456,16 +2456,16 @@
         <v>0.0</v>
       </c>
       <c r="N30" s="2">
-        <v>229.0</v>
+        <v>233.0</v>
       </c>
       <c r="O30" s="2">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="P30" s="2">
         <v>78.0</v>
       </c>
       <c r="Q30" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="R30" s="2">
         <v>2.0</v>
@@ -2515,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>679.0</v>
+        <v>814.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2527,22 +2527,22 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>679.0</v>
+        <v>814.0</v>
       </c>
       <c r="O31" s="2">
-        <v>342.0</v>
+        <v>433.0</v>
       </c>
       <c r="P31" s="2">
-        <v>332.0</v>
+        <v>376.0</v>
       </c>
       <c r="Q31" s="2">
         <v>5.0</v>
       </c>
       <c r="R31" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S31" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T31" s="2">
         <v>0.0</v>
@@ -2554,7 +2554,7 @@
         <v>0.0</v>
       </c>
       <c r="W31" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -2586,7 +2586,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" s="2">
-        <v>696.0</v>
+        <v>734.0</v>
       </c>
       <c r="K32" s="2">
         <v>1.0</v>
@@ -2598,13 +2598,13 @@
         <v>0.0</v>
       </c>
       <c r="N32" s="2">
-        <v>696.0</v>
+        <v>734.0</v>
       </c>
       <c r="O32" s="2">
-        <v>333.0</v>
+        <v>355.0</v>
       </c>
       <c r="P32" s="2">
-        <v>342.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q32" s="2">
         <v>21.0</v>
@@ -2657,7 +2657,7 @@
         <v>346.0</v>
       </c>
       <c r="J33" s="2">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
       <c r="K33" s="2">
         <v>1.0</v>
@@ -2669,10 +2669,10 @@
         <v>0.0</v>
       </c>
       <c r="N33" s="2">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
       <c r="O33" s="2">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="P33" s="2">
         <v>171.0</v>
@@ -2728,7 +2728,7 @@
         <v>647.0</v>
       </c>
       <c r="J34" s="2">
-        <v>612.0</v>
+        <v>624.0</v>
       </c>
       <c r="K34" s="2">
         <v>1.0</v>
@@ -2740,13 +2740,13 @@
         <v>0.0</v>
       </c>
       <c r="N34" s="2">
-        <v>612.0</v>
+        <v>624.0</v>
       </c>
       <c r="O34" s="2">
-        <v>343.0</v>
+        <v>354.0</v>
       </c>
       <c r="P34" s="2">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="Q34" s="2">
         <v>0.0</v>
@@ -2799,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>400.0</v>
+        <v>449.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2811,13 +2811,13 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>400.0</v>
+        <v>449.0</v>
       </c>
       <c r="O35" s="2">
-        <v>208.0</v>
+        <v>237.0</v>
       </c>
       <c r="P35" s="2">
-        <v>183.0</v>
+        <v>203.0</v>
       </c>
       <c r="Q35" s="2">
         <v>9.0</v>
@@ -2870,7 +2870,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>530.0</v>
+        <v>604.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2882,16 +2882,16 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>530.0</v>
+        <v>604.0</v>
       </c>
       <c r="O36" s="2">
-        <v>228.0</v>
+        <v>278.0</v>
       </c>
       <c r="P36" s="2">
-        <v>302.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q36" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="R36" s="2">
         <v>45.0</v>
@@ -2903,13 +2903,13 @@
         <v>0.0</v>
       </c>
       <c r="U36" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="V36" s="2">
         <v>0.0</v>
       </c>
       <c r="W36" s="2">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -2941,7 +2941,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" s="2">
-        <v>450.0</v>
+        <v>462.0</v>
       </c>
       <c r="K37" s="2">
         <v>1.0</v>
@@ -2953,22 +2953,22 @@
         <v>0.0</v>
       </c>
       <c r="N37" s="2">
-        <v>450.0</v>
+        <v>462.0</v>
       </c>
       <c r="O37" s="2">
-        <v>233.0</v>
+        <v>241.0</v>
       </c>
       <c r="P37" s="2">
-        <v>213.0</v>
+        <v>217.0</v>
       </c>
       <c r="Q37" s="2">
         <v>4.0</v>
       </c>
       <c r="R37" s="2">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="S37" s="2">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="T37" s="2">
         <v>0.0</v>
@@ -2980,7 +2980,7 @@
         <v>0.0</v>
       </c>
       <c r="W37" s="2">
-        <v>0.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -3012,7 +3012,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" s="2">
-        <v>945.0</v>
+        <v>949.0</v>
       </c>
       <c r="K38" s="2">
         <v>1.0</v>
@@ -3024,13 +3024,13 @@
         <v>0.0</v>
       </c>
       <c r="N38" s="2">
-        <v>945.0</v>
+        <v>949.0</v>
       </c>
       <c r="O38" s="2">
-        <v>553.0</v>
+        <v>555.0</v>
       </c>
       <c r="P38" s="2">
-        <v>392.0</v>
+        <v>394.0</v>
       </c>
       <c r="Q38" s="2">
         <v>0.0</v>
@@ -3083,7 +3083,7 @@
         <v>588.0</v>
       </c>
       <c r="J39" s="2">
-        <v>408.0</v>
+        <v>434.0</v>
       </c>
       <c r="K39" s="2">
         <v>1.0</v>
@@ -3095,13 +3095,13 @@
         <v>0.0</v>
       </c>
       <c r="N39" s="2">
-        <v>408.0</v>
+        <v>434.0</v>
       </c>
       <c r="O39" s="2">
-        <v>203.0</v>
+        <v>218.0</v>
       </c>
       <c r="P39" s="2">
-        <v>205.0</v>
+        <v>216.0</v>
       </c>
       <c r="Q39" s="2">
         <v>0.0</v>
@@ -3296,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>524.0</v>
+        <v>565.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3308,13 +3308,13 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>524.0</v>
+        <v>565.0</v>
       </c>
       <c r="O42" s="2">
-        <v>341.0</v>
+        <v>370.0</v>
       </c>
       <c r="P42" s="2">
-        <v>183.0</v>
+        <v>195.0</v>
       </c>
       <c r="Q42" s="2">
         <v>0.0</v>
@@ -3438,7 +3438,7 @@
         <v>1094.0</v>
       </c>
       <c r="J44" s="2">
-        <v>956.0</v>
+        <v>1044.0</v>
       </c>
       <c r="K44" s="2">
         <v>1.0</v>
@@ -3450,34 +3450,34 @@
         <v>0.0</v>
       </c>
       <c r="N44" s="2">
-        <v>956.0</v>
+        <v>1044.0</v>
       </c>
       <c r="O44" s="2">
-        <v>489.0</v>
+        <v>563.0</v>
       </c>
       <c r="P44" s="2">
-        <v>466.0</v>
+        <v>480.0</v>
       </c>
       <c r="Q44" s="2">
         <v>1.0</v>
       </c>
       <c r="R44" s="2">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="S44" s="2">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="T44" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U44" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="V44" s="2">
         <v>0.0</v>
       </c>
       <c r="W44" s="2">
-        <v>0.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -3509,7 +3509,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>1037.0</v>
+        <v>1043.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3521,13 +3521,13 @@
         <v>1.0</v>
       </c>
       <c r="N45" s="2">
-        <v>1036.0</v>
+        <v>1042.0</v>
       </c>
       <c r="O45" s="2">
-        <v>485.0</v>
+        <v>488.0</v>
       </c>
       <c r="P45" s="2">
-        <v>521.0</v>
+        <v>524.0</v>
       </c>
       <c r="Q45" s="2">
         <v>31.0</v>
@@ -3580,7 +3580,7 @@
         <v>1429.0</v>
       </c>
       <c r="J46" s="2">
-        <v>1361.0</v>
+        <v>1363.0</v>
       </c>
       <c r="K46" s="2">
         <v>1.0</v>
@@ -3592,22 +3592,22 @@
         <v>0.0</v>
       </c>
       <c r="N46" s="2">
-        <v>1361.0</v>
+        <v>1363.0</v>
       </c>
       <c r="O46" s="2">
         <v>706.0</v>
       </c>
       <c r="P46" s="2">
-        <v>608.0</v>
+        <v>609.0</v>
       </c>
       <c r="Q46" s="2">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="R46" s="2">
         <v>15.0</v>
       </c>
       <c r="S46" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="T46" s="2">
         <v>18.0</v>
@@ -3619,7 +3619,7 @@
         <v>0.0</v>
       </c>
       <c r="W46" s="2">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3722,7 +3722,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>902.0</v>
+        <v>914.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3734,10 +3734,10 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>902.0</v>
+        <v>914.0</v>
       </c>
       <c r="O48" s="2">
-        <v>518.0</v>
+        <v>530.0</v>
       </c>
       <c r="P48" s="2">
         <v>384.0</v>
@@ -3746,7 +3746,7 @@
         <v>0.0</v>
       </c>
       <c r="R48" s="2">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="S48" s="2">
         <v>0.0</v>
@@ -3761,7 +3761,7 @@
         <v>0.0</v>
       </c>
       <c r="W48" s="2">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -3793,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>957.0</v>
+        <v>1019.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3805,22 +3805,22 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>957.0</v>
+        <v>1019.0</v>
       </c>
       <c r="O49" s="2">
-        <v>509.0</v>
+        <v>534.0</v>
       </c>
       <c r="P49" s="2">
-        <v>438.0</v>
+        <v>453.0</v>
       </c>
       <c r="Q49" s="2">
-        <v>10.0</v>
+        <v>32.0</v>
       </c>
       <c r="R49" s="2">
-        <v>34.0</v>
+        <v>50.0</v>
       </c>
       <c r="S49" s="2">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="T49" s="2">
         <v>0.0</v>
@@ -3832,7 +3832,7 @@
         <v>0.0</v>
       </c>
       <c r="W49" s="2">
-        <v>38.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -3864,7 +3864,7 @@
         <v>582.0</v>
       </c>
       <c r="J50" s="2">
-        <v>471.0</v>
+        <v>518.0</v>
       </c>
       <c r="K50" s="2">
         <v>1.0</v>
@@ -3876,13 +3876,13 @@
         <v>3.0</v>
       </c>
       <c r="N50" s="2">
-        <v>468.0</v>
+        <v>515.0</v>
       </c>
       <c r="O50" s="2">
-        <v>216.0</v>
+        <v>258.0</v>
       </c>
       <c r="P50" s="2">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="Q50" s="2">
         <v>28.0</v>
@@ -3891,7 +3891,7 @@
         <v>13.0</v>
       </c>
       <c r="S50" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T50" s="2">
         <v>0.0</v>
@@ -3903,7 +3903,7 @@
         <v>0.0</v>
       </c>
       <c r="W50" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -3935,7 +3935,7 @@
         <v>878.0</v>
       </c>
       <c r="J51" s="2">
-        <v>701.0</v>
+        <v>779.0</v>
       </c>
       <c r="K51" s="2">
         <v>1.0</v>
@@ -3947,13 +3947,13 @@
         <v>0.0</v>
       </c>
       <c r="N51" s="2">
-        <v>701.0</v>
+        <v>779.0</v>
       </c>
       <c r="O51" s="2">
-        <v>294.0</v>
+        <v>366.0</v>
       </c>
       <c r="P51" s="2">
-        <v>407.0</v>
+        <v>413.0</v>
       </c>
       <c r="Q51" s="2">
         <v>0.0</v>
@@ -3962,10 +3962,10 @@
         <v>0.0</v>
       </c>
       <c r="S51" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="T51" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U51" s="2">
         <v>0.0</v>
@@ -3974,7 +3974,7 @@
         <v>0.0</v>
       </c>
       <c r="W51" s="2">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
@@ -4006,7 +4006,7 @@
         <v>605.0</v>
       </c>
       <c r="J52" s="2">
-        <v>537.0</v>
+        <v>576.0</v>
       </c>
       <c r="K52" s="2">
         <v>1.0</v>
@@ -4018,19 +4018,19 @@
         <v>0.0</v>
       </c>
       <c r="N52" s="2">
-        <v>537.0</v>
+        <v>576.0</v>
       </c>
       <c r="O52" s="2">
-        <v>261.0</v>
+        <v>285.0</v>
       </c>
       <c r="P52" s="2">
-        <v>276.0</v>
+        <v>291.0</v>
       </c>
       <c r="Q52" s="2">
         <v>0.0</v>
       </c>
       <c r="R52" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="S52" s="2">
         <v>3.0</v>
@@ -4045,7 +4045,7 @@
         <v>0.0</v>
       </c>
       <c r="W52" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
@@ -4101,7 +4101,7 @@
         <v>5.0</v>
       </c>
       <c r="R53" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S53" s="2">
         <v>3.0</v>
@@ -4116,7 +4116,7 @@
         <v>0.0</v>
       </c>
       <c r="W53" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
@@ -4148,7 +4148,7 @@
         <v>778.0</v>
       </c>
       <c r="J54" s="2">
-        <v>606.0</v>
+        <v>613.0</v>
       </c>
       <c r="K54" s="2">
         <v>1.0</v>
@@ -4160,22 +4160,22 @@
         <v>0.0</v>
       </c>
       <c r="N54" s="2">
-        <v>606.0</v>
+        <v>613.0</v>
       </c>
       <c r="O54" s="2">
-        <v>318.0</v>
+        <v>322.0</v>
       </c>
       <c r="P54" s="2">
-        <v>283.0</v>
+        <v>285.0</v>
       </c>
       <c r="Q54" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R54" s="2">
         <v>0.0</v>
       </c>
       <c r="S54" s="2">
-        <v>0.0</v>
+        <v>104.0</v>
       </c>
       <c r="T54" s="2">
         <v>0.0</v>
@@ -4187,7 +4187,7 @@
         <v>0.0</v>
       </c>
       <c r="W54" s="2">
-        <v>0.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
@@ -4219,7 +4219,7 @@
         <v>540.0</v>
       </c>
       <c r="J55" s="2">
-        <v>391.0</v>
+        <v>405.0</v>
       </c>
       <c r="K55" s="2">
         <v>1.0</v>
@@ -4231,22 +4231,22 @@
         <v>0.0</v>
       </c>
       <c r="N55" s="2">
-        <v>391.0</v>
+        <v>405.0</v>
       </c>
       <c r="O55" s="2">
-        <v>168.0</v>
+        <v>176.0</v>
       </c>
       <c r="P55" s="2">
-        <v>223.0</v>
+        <v>229.0</v>
       </c>
       <c r="Q55" s="2">
         <v>0.0</v>
       </c>
       <c r="R55" s="2">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="S55" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="T55" s="2">
         <v>0.0</v>
@@ -4258,7 +4258,7 @@
         <v>0.0</v>
       </c>
       <c r="W55" s="2">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
@@ -4290,7 +4290,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" s="2">
-        <v>568.0</v>
+        <v>570.0</v>
       </c>
       <c r="K56" s="2">
         <v>1.0</v>
@@ -4302,10 +4302,10 @@
         <v>0.0</v>
       </c>
       <c r="N56" s="2">
-        <v>568.0</v>
+        <v>570.0</v>
       </c>
       <c r="O56" s="2">
-        <v>282.0</v>
+        <v>284.0</v>
       </c>
       <c r="P56" s="2">
         <v>286.0</v>
@@ -4361,7 +4361,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" s="2">
-        <v>528.0</v>
+        <v>545.0</v>
       </c>
       <c r="K57" s="2">
         <v>1.0</v>
@@ -4373,10 +4373,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" s="2">
-        <v>528.0</v>
+        <v>545.0</v>
       </c>
       <c r="O57" s="2">
-        <v>528.0</v>
+        <v>545.0</v>
       </c>
       <c r="P57" s="2">
         <v>0.0</v>
@@ -4432,7 +4432,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" s="2">
-        <v>833.0</v>
+        <v>853.0</v>
       </c>
       <c r="K58" s="2">
         <v>1.0</v>
@@ -4444,13 +4444,13 @@
         <v>0.0</v>
       </c>
       <c r="N58" s="2">
-        <v>833.0</v>
+        <v>853.0</v>
       </c>
       <c r="O58" s="2">
-        <v>442.0</v>
+        <v>451.0</v>
       </c>
       <c r="P58" s="2">
-        <v>391.0</v>
+        <v>402.0</v>
       </c>
       <c r="Q58" s="2">
         <v>0.0</v>
@@ -4503,7 +4503,7 @@
         <v>909.0</v>
       </c>
       <c r="J59" s="2">
-        <v>672.0</v>
+        <v>674.0</v>
       </c>
       <c r="K59" s="2">
         <v>1.0</v>
@@ -4515,25 +4515,25 @@
         <v>0.0</v>
       </c>
       <c r="N59" s="2">
-        <v>672.0</v>
+        <v>674.0</v>
       </c>
       <c r="O59" s="2">
-        <v>324.0</v>
+        <v>325.0</v>
       </c>
       <c r="P59" s="2">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q59" s="2">
         <v>0.0</v>
       </c>
       <c r="R59" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="S59" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T59" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U59" s="2">
         <v>0.0</v>
@@ -4542,7 +4542,7 @@
         <v>0.0</v>
       </c>
       <c r="W59" s="2">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -4574,7 +4574,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" s="2">
-        <v>607.0</v>
+        <v>616.0</v>
       </c>
       <c r="K60" s="2">
         <v>1.0</v>
@@ -4586,13 +4586,13 @@
         <v>0.0</v>
       </c>
       <c r="N60" s="2">
-        <v>607.0</v>
+        <v>616.0</v>
       </c>
       <c r="O60" s="2">
-        <v>268.0</v>
+        <v>272.0</v>
       </c>
       <c r="P60" s="2">
-        <v>339.0</v>
+        <v>344.0</v>
       </c>
       <c r="Q60" s="2">
         <v>0.0</v>
@@ -4601,7 +4601,7 @@
         <v>12.0</v>
       </c>
       <c r="S60" s="2">
-        <v>6.0</v>
+        <v>19.0</v>
       </c>
       <c r="T60" s="2">
         <v>4.0</v>
@@ -4613,7 +4613,7 @@
         <v>0.0</v>
       </c>
       <c r="W60" s="2">
-        <v>29.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -4645,7 +4645,7 @@
         <v>1075.0</v>
       </c>
       <c r="J61" s="2">
-        <v>799.0</v>
+        <v>855.0</v>
       </c>
       <c r="K61" s="2">
         <v>1.0</v>
@@ -4657,22 +4657,22 @@
         <v>0.0</v>
       </c>
       <c r="N61" s="2">
-        <v>799.0</v>
+        <v>855.0</v>
       </c>
       <c r="O61" s="2">
-        <v>401.0</v>
+        <v>445.0</v>
       </c>
       <c r="P61" s="2">
-        <v>398.0</v>
+        <v>410.0</v>
       </c>
       <c r="Q61" s="2">
         <v>0.0</v>
       </c>
       <c r="R61" s="2">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="S61" s="2">
-        <v>2.0</v>
+        <v>43.0</v>
       </c>
       <c r="T61" s="2">
         <v>0.0</v>
@@ -4684,7 +4684,7 @@
         <v>0.0</v>
       </c>
       <c r="W61" s="2">
-        <v>46.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
@@ -4716,7 +4716,7 @@
         <v>570.0</v>
       </c>
       <c r="J62" s="2">
-        <v>508.0</v>
+        <v>511.0</v>
       </c>
       <c r="K62" s="2">
         <v>1.0</v>
@@ -4728,10 +4728,10 @@
         <v>0.0</v>
       </c>
       <c r="N62" s="2">
-        <v>508.0</v>
+        <v>511.0</v>
       </c>
       <c r="O62" s="2">
-        <v>276.0</v>
+        <v>279.0</v>
       </c>
       <c r="P62" s="2">
         <v>231.0</v>
@@ -4787,7 +4787,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" s="2">
-        <v>758.0</v>
+        <v>843.0</v>
       </c>
       <c r="K63" s="2">
         <v>1.0</v>
@@ -4799,22 +4799,22 @@
         <v>0.0</v>
       </c>
       <c r="N63" s="2">
-        <v>758.0</v>
+        <v>843.0</v>
       </c>
       <c r="O63" s="2">
-        <v>409.0</v>
+        <v>487.0</v>
       </c>
       <c r="P63" s="2">
-        <v>348.0</v>
+        <v>355.0</v>
       </c>
       <c r="Q63" s="2">
         <v>1.0</v>
       </c>
       <c r="R63" s="2">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="S63" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T63" s="2">
         <v>0.0</v>
@@ -4826,7 +4826,7 @@
         <v>0.0</v>
       </c>
       <c r="W63" s="2">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
@@ -4858,7 +4858,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" s="2">
-        <v>1042.0</v>
+        <v>1066.0</v>
       </c>
       <c r="K64" s="2">
         <v>1.0</v>
@@ -4870,13 +4870,13 @@
         <v>0.0</v>
       </c>
       <c r="N64" s="2">
-        <v>1042.0</v>
+        <v>1066.0</v>
       </c>
       <c r="O64" s="2">
-        <v>588.0</v>
+        <v>608.0</v>
       </c>
       <c r="P64" s="2">
-        <v>454.0</v>
+        <v>458.0</v>
       </c>
       <c r="Q64" s="2">
         <v>0.0</v>
@@ -5030,7 +5030,7 @@
         <v>51.0</v>
       </c>
       <c r="T66" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U66" s="2">
         <v>0.0</v>
@@ -5039,7 +5039,7 @@
         <v>0.0</v>
       </c>
       <c r="W66" s="2">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
@@ -5071,7 +5071,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" s="2">
-        <v>925.0</v>
+        <v>957.0</v>
       </c>
       <c r="K67" s="2">
         <v>1.0</v>
@@ -5083,19 +5083,19 @@
         <v>0.0</v>
       </c>
       <c r="N67" s="2">
-        <v>925.0</v>
+        <v>957.0</v>
       </c>
       <c r="O67" s="2">
-        <v>422.0</v>
+        <v>451.0</v>
       </c>
       <c r="P67" s="2">
-        <v>502.0</v>
+        <v>504.0</v>
       </c>
       <c r="Q67" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R67" s="2">
-        <v>0.0</v>
+        <v>58.0</v>
       </c>
       <c r="S67" s="2">
         <v>1.0</v>
@@ -5110,7 +5110,7 @@
         <v>0.0</v>
       </c>
       <c r="W67" s="2">
-        <v>1.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -5142,7 +5142,7 @@
         <v>1042.0</v>
       </c>
       <c r="J68" s="2">
-        <v>983.0</v>
+        <v>989.0</v>
       </c>
       <c r="K68" s="2">
         <v>1.0</v>
@@ -5154,25 +5154,25 @@
         <v>0.0</v>
       </c>
       <c r="N68" s="2">
-        <v>983.0</v>
+        <v>989.0</v>
       </c>
       <c r="O68" s="2">
-        <v>529.0</v>
+        <v>531.0</v>
       </c>
       <c r="P68" s="2">
         <v>439.0</v>
       </c>
       <c r="Q68" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="R68" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="S68" s="2">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="T68" s="2">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="U68" s="2">
         <v>0.0</v>
@@ -5181,7 +5181,7 @@
         <v>0.0</v>
       </c>
       <c r="W68" s="2">
-        <v>16.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
@@ -5210,10 +5210,10 @@
         <v>1125.0</v>
       </c>
       <c r="I69" s="2">
-        <v>1122.0</v>
+        <v>1124.0</v>
       </c>
       <c r="J69" s="2">
-        <v>983.0</v>
+        <v>1007.0</v>
       </c>
       <c r="K69" s="2">
         <v>1.0</v>
@@ -5225,13 +5225,13 @@
         <v>1.0</v>
       </c>
       <c r="N69" s="2">
-        <v>982.0</v>
+        <v>1006.0</v>
       </c>
       <c r="O69" s="2">
-        <v>508.0</v>
+        <v>528.0</v>
       </c>
       <c r="P69" s="2">
-        <v>475.0</v>
+        <v>479.0</v>
       </c>
       <c r="Q69" s="2">
         <v>0.0</v>
@@ -5284,7 +5284,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" s="2">
-        <v>1061.0</v>
+        <v>1070.0</v>
       </c>
       <c r="K70" s="2">
         <v>1.0</v>
@@ -5296,13 +5296,13 @@
         <v>0.0</v>
       </c>
       <c r="N70" s="2">
-        <v>1061.0</v>
+        <v>1070.0</v>
       </c>
       <c r="O70" s="2">
-        <v>658.0</v>
+        <v>659.0</v>
       </c>
       <c r="P70" s="2">
-        <v>393.0</v>
+        <v>401.0</v>
       </c>
       <c r="Q70" s="2">
         <v>10.0</v>
@@ -5317,13 +5317,13 @@
         <v>0.0</v>
       </c>
       <c r="U70" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="V70" s="2">
         <v>0.0</v>
       </c>
       <c r="W70" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -5426,7 +5426,7 @@
         <v>1141.0</v>
       </c>
       <c r="J72" s="2">
-        <v>1065.0</v>
+        <v>1067.0</v>
       </c>
       <c r="K72" s="2">
         <v>1.0</v>
@@ -5438,10 +5438,10 @@
         <v>0.0</v>
       </c>
       <c r="N72" s="2">
-        <v>1065.0</v>
+        <v>1067.0</v>
       </c>
       <c r="O72" s="2">
-        <v>660.0</v>
+        <v>662.0</v>
       </c>
       <c r="P72" s="2">
         <v>397.0</v>
@@ -5497,7 +5497,7 @@
         <v>973.0</v>
       </c>
       <c r="J73" s="2">
-        <v>922.0</v>
+        <v>941.0</v>
       </c>
       <c r="K73" s="2">
         <v>1.0</v>
@@ -5509,19 +5509,19 @@
         <v>0.0</v>
       </c>
       <c r="N73" s="2">
-        <v>922.0</v>
+        <v>941.0</v>
       </c>
       <c r="O73" s="2">
-        <v>472.0</v>
+        <v>488.0</v>
       </c>
       <c r="P73" s="2">
         <v>443.0</v>
       </c>
       <c r="Q73" s="2">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="R73" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="S73" s="2">
         <v>0.0</v>
@@ -5536,7 +5536,7 @@
         <v>0.0</v>
       </c>
       <c r="W73" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
@@ -5568,7 +5568,7 @@
         <v>760.0</v>
       </c>
       <c r="J74" s="2">
-        <v>715.0</v>
+        <v>733.0</v>
       </c>
       <c r="K74" s="2">
         <v>1.0</v>
@@ -5580,34 +5580,34 @@
         <v>0.0</v>
       </c>
       <c r="N74" s="2">
-        <v>715.0</v>
+        <v>733.0</v>
       </c>
       <c r="O74" s="2">
-        <v>398.0</v>
+        <v>403.0</v>
       </c>
       <c r="P74" s="2">
-        <v>315.0</v>
+        <v>320.0</v>
       </c>
       <c r="Q74" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="R74" s="2">
         <v>14.0</v>
       </c>
       <c r="S74" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="T74" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U74" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="V74" s="2">
         <v>0.0</v>
       </c>
       <c r="W74" s="2">
-        <v>14.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
@@ -5639,7 +5639,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" s="2">
-        <v>812.0</v>
+        <v>815.0</v>
       </c>
       <c r="K75" s="2">
         <v>1.0</v>
@@ -5651,16 +5651,16 @@
         <v>0.0</v>
       </c>
       <c r="N75" s="2">
-        <v>812.0</v>
+        <v>815.0</v>
       </c>
       <c r="O75" s="2">
         <v>425.0</v>
       </c>
       <c r="P75" s="2">
-        <v>377.0</v>
+        <v>378.0</v>
       </c>
       <c r="Q75" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R75" s="2">
         <v>4.0</v>
@@ -5710,7 +5710,7 @@
         <v>970.0</v>
       </c>
       <c r="J76" s="2">
-        <v>803.0</v>
+        <v>845.0</v>
       </c>
       <c r="K76" s="2">
         <v>1.0</v>
@@ -5722,13 +5722,13 @@
         <v>0.0</v>
       </c>
       <c r="N76" s="2">
-        <v>803.0</v>
+        <v>845.0</v>
       </c>
       <c r="O76" s="2">
-        <v>434.0</v>
+        <v>463.0</v>
       </c>
       <c r="P76" s="2">
-        <v>369.0</v>
+        <v>382.0</v>
       </c>
       <c r="Q76" s="2">
         <v>0.0</v>
@@ -5737,19 +5737,19 @@
         <v>0.0</v>
       </c>
       <c r="S76" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T76" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="U76" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V76" s="2">
         <v>0.0</v>
       </c>
       <c r="W76" s="2">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
@@ -5781,7 +5781,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" s="2">
-        <v>504.0</v>
+        <v>571.0</v>
       </c>
       <c r="K77" s="2">
         <v>1.0</v>
@@ -5793,16 +5793,16 @@
         <v>0.0</v>
       </c>
       <c r="N77" s="2">
-        <v>504.0</v>
+        <v>571.0</v>
       </c>
       <c r="O77" s="2">
-        <v>58.0</v>
+        <v>106.0</v>
       </c>
       <c r="P77" s="2">
-        <v>303.0</v>
+        <v>308.0</v>
       </c>
       <c r="Q77" s="2">
-        <v>143.0</v>
+        <v>157.0</v>
       </c>
       <c r="R77" s="2">
         <v>0.0</v>
@@ -5852,7 +5852,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>514.0</v>
+        <v>576.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5864,13 +5864,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>514.0</v>
+        <v>576.0</v>
       </c>
       <c r="O78" s="2">
-        <v>166.0</v>
+        <v>180.0</v>
       </c>
       <c r="P78" s="2">
-        <v>348.0</v>
+        <v>396.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
@@ -5923,7 +5923,7 @@
         <v>786.0</v>
       </c>
       <c r="J79" s="2">
-        <v>354.0</v>
+        <v>427.0</v>
       </c>
       <c r="K79" s="2">
         <v>1.0</v>
@@ -5935,13 +5935,13 @@
         <v>0.0</v>
       </c>
       <c r="N79" s="2">
-        <v>354.0</v>
+        <v>427.0</v>
       </c>
       <c r="O79" s="2">
-        <v>140.0</v>
+        <v>208.0</v>
       </c>
       <c r="P79" s="2">
-        <v>214.0</v>
+        <v>219.0</v>
       </c>
       <c r="Q79" s="2">
         <v>0.0</v>
@@ -5994,7 +5994,7 @@
         <v>1333.0</v>
       </c>
       <c r="J80" s="2">
-        <v>841.0</v>
+        <v>936.0</v>
       </c>
       <c r="K80" s="2">
         <v>1.0</v>
@@ -6006,16 +6006,16 @@
         <v>0.0</v>
       </c>
       <c r="N80" s="2">
-        <v>841.0</v>
+        <v>936.0</v>
       </c>
       <c r="O80" s="2">
-        <v>461.0</v>
+        <v>517.0</v>
       </c>
       <c r="P80" s="2">
-        <v>380.0</v>
+        <v>415.0</v>
       </c>
       <c r="Q80" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="R80" s="2">
         <v>0.0</v>
@@ -6065,7 +6065,7 @@
         <v>796.0</v>
       </c>
       <c r="J81" s="2">
-        <v>700.0</v>
+        <v>703.0</v>
       </c>
       <c r="K81" s="2">
         <v>1.0</v>
@@ -6077,13 +6077,13 @@
         <v>0.0</v>
       </c>
       <c r="N81" s="2">
-        <v>700.0</v>
+        <v>703.0</v>
       </c>
       <c r="O81" s="2">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
       <c r="P81" s="2">
-        <v>334.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q81" s="2">
         <v>0.0</v>
@@ -6136,7 +6136,7 @@
         <v>1157.0</v>
       </c>
       <c r="J82" s="2">
-        <v>841.0</v>
+        <v>853.0</v>
       </c>
       <c r="K82" s="2">
         <v>1.0</v>
@@ -6148,22 +6148,22 @@
         <v>0.0</v>
       </c>
       <c r="N82" s="2">
-        <v>841.0</v>
+        <v>853.0</v>
       </c>
       <c r="O82" s="2">
-        <v>397.0</v>
+        <v>404.0</v>
       </c>
       <c r="P82" s="2">
-        <v>444.0</v>
+        <v>449.0</v>
       </c>
       <c r="Q82" s="2">
         <v>0.0</v>
       </c>
       <c r="R82" s="2">
-        <v>1.0</v>
+        <v>37.0</v>
       </c>
       <c r="S82" s="2">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="T82" s="2">
         <v>0.0</v>
@@ -6175,7 +6175,7 @@
         <v>0.0</v>
       </c>
       <c r="W82" s="2">
-        <v>1.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
@@ -6231,10 +6231,10 @@
         <v>0.0</v>
       </c>
       <c r="R83" s="2">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="S83" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T83" s="2">
         <v>0.0</v>
@@ -6246,7 +6246,7 @@
         <v>0.0</v>
       </c>
       <c r="W83" s="2">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -6278,7 +6278,7 @@
         <v>451.0</v>
       </c>
       <c r="J84" s="2">
-        <v>380.0</v>
+        <v>385.0</v>
       </c>
       <c r="K84" s="2">
         <v>1.0</v>
@@ -6290,34 +6290,34 @@
         <v>0.0</v>
       </c>
       <c r="N84" s="2">
-        <v>380.0</v>
+        <v>385.0</v>
       </c>
       <c r="O84" s="2">
-        <v>178.0</v>
+        <v>181.0</v>
       </c>
       <c r="P84" s="2">
-        <v>202.0</v>
+        <v>204.0</v>
       </c>
       <c r="Q84" s="2">
         <v>0.0</v>
       </c>
       <c r="R84" s="2">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="S84" s="2">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="T84" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U84" s="2">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="V84" s="2">
         <v>0.0</v>
       </c>
       <c r="W84" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
@@ -6349,7 +6349,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" s="2">
-        <v>1077.0</v>
+        <v>1122.0</v>
       </c>
       <c r="K85" s="2">
         <v>1.0</v>
@@ -6361,34 +6361,34 @@
         <v>0.0</v>
       </c>
       <c r="N85" s="2">
-        <v>1077.0</v>
+        <v>1122.0</v>
       </c>
       <c r="O85" s="2">
-        <v>519.0</v>
+        <v>548.0</v>
       </c>
       <c r="P85" s="2">
-        <v>558.0</v>
+        <v>572.0</v>
       </c>
       <c r="Q85" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R85" s="2">
-        <v>19.0</v>
+        <v>42.0</v>
       </c>
       <c r="S85" s="2">
-        <v>10.0</v>
+        <v>22.0</v>
       </c>
       <c r="T85" s="2">
         <v>0.0</v>
       </c>
       <c r="U85" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="V85" s="2">
         <v>0.0</v>
       </c>
       <c r="W85" s="2">
-        <v>30.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
@@ -6420,7 +6420,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" s="2">
-        <v>923.0</v>
+        <v>1032.0</v>
       </c>
       <c r="K86" s="2">
         <v>1.0</v>
@@ -6432,13 +6432,13 @@
         <v>0.0</v>
       </c>
       <c r="N86" s="2">
-        <v>923.0</v>
+        <v>1032.0</v>
       </c>
       <c r="O86" s="2">
-        <v>439.0</v>
+        <v>524.0</v>
       </c>
       <c r="P86" s="2">
-        <v>484.0</v>
+        <v>508.0</v>
       </c>
       <c r="Q86" s="2">
         <v>0.0</v>
@@ -6491,7 +6491,7 @@
         <v>735.0</v>
       </c>
       <c r="J87" s="2">
-        <v>671.0</v>
+        <v>693.0</v>
       </c>
       <c r="K87" s="2">
         <v>1.0</v>
@@ -6503,13 +6503,13 @@
         <v>0.0</v>
       </c>
       <c r="N87" s="2">
-        <v>671.0</v>
+        <v>693.0</v>
       </c>
       <c r="O87" s="2">
-        <v>337.0</v>
+        <v>353.0</v>
       </c>
       <c r="P87" s="2">
-        <v>334.0</v>
+        <v>340.0</v>
       </c>
       <c r="Q87" s="2">
         <v>0.0</v>
@@ -6518,10 +6518,10 @@
         <v>21.0</v>
       </c>
       <c r="S87" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="T87" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U87" s="2">
         <v>4.0</v>
@@ -6530,7 +6530,7 @@
         <v>0.0</v>
       </c>
       <c r="W87" s="2">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
@@ -6562,7 +6562,7 @@
         <v>882.0</v>
       </c>
       <c r="J88" s="2">
-        <v>609.0</v>
+        <v>655.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6574,13 +6574,13 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>609.0</v>
+        <v>655.0</v>
       </c>
       <c r="O88" s="2">
-        <v>282.0</v>
+        <v>326.0</v>
       </c>
       <c r="P88" s="2">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q88" s="2">
         <v>0.0</v>
@@ -6633,7 +6633,7 @@
         <v>814.0</v>
       </c>
       <c r="J89" s="2">
-        <v>475.0</v>
+        <v>566.0</v>
       </c>
       <c r="K89" s="2">
         <v>1.0</v>
@@ -6645,13 +6645,13 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>475.0</v>
+        <v>566.0</v>
       </c>
       <c r="O89" s="2">
-        <v>208.0</v>
+        <v>296.0</v>
       </c>
       <c r="P89" s="2">
-        <v>267.0</v>
+        <v>270.0</v>
       </c>
       <c r="Q89" s="2">
         <v>0.0</v>
@@ -6704,7 +6704,7 @@
         <v>744.0</v>
       </c>
       <c r="J90" s="2">
-        <v>660.0</v>
+        <v>662.0</v>
       </c>
       <c r="K90" s="2">
         <v>1.0</v>
@@ -6716,13 +6716,13 @@
         <v>0.0</v>
       </c>
       <c r="N90" s="2">
-        <v>660.0</v>
+        <v>662.0</v>
       </c>
       <c r="O90" s="2">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
       <c r="P90" s="2">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q90" s="2">
         <v>2.0</v>
@@ -6775,7 +6775,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>651.0</v>
+        <v>670.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -6787,16 +6787,16 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>651.0</v>
+        <v>670.0</v>
       </c>
       <c r="O91" s="2">
-        <v>129.0</v>
+        <v>144.0</v>
       </c>
       <c r="P91" s="2">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>203.0</v>
+        <v>206.0</v>
       </c>
       <c r="R91" s="2">
         <v>43.0</v>
@@ -6805,16 +6805,16 @@
         <v>33.0</v>
       </c>
       <c r="T91" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U91" s="2">
-        <v>109.0</v>
+        <v>126.0</v>
       </c>
       <c r="V91" s="2">
         <v>1.0</v>
       </c>
       <c r="W91" s="2">
-        <v>187.0</v>
+        <v>205.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
@@ -6846,7 +6846,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" s="2">
-        <v>641.0</v>
+        <v>691.0</v>
       </c>
       <c r="K92" s="2">
         <v>1.0</v>
@@ -6858,22 +6858,22 @@
         <v>0.0</v>
       </c>
       <c r="N92" s="2">
-        <v>641.0</v>
+        <v>691.0</v>
       </c>
       <c r="O92" s="2">
-        <v>264.0</v>
+        <v>298.0</v>
       </c>
       <c r="P92" s="2">
-        <v>286.0</v>
+        <v>296.0</v>
       </c>
       <c r="Q92" s="2">
-        <v>91.0</v>
+        <v>97.0</v>
       </c>
       <c r="R92" s="2">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
       <c r="S92" s="2">
-        <v>80.0</v>
+        <v>95.0</v>
       </c>
       <c r="T92" s="2">
         <v>10.0</v>
@@ -6885,7 +6885,7 @@
         <v>2.0</v>
       </c>
       <c r="W92" s="2">
-        <v>139.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
@@ -6917,7 +6917,7 @@
         <v>960.0</v>
       </c>
       <c r="J93" s="2">
-        <v>768.0</v>
+        <v>810.0</v>
       </c>
       <c r="K93" s="2">
         <v>1.0</v>
@@ -6929,25 +6929,25 @@
         <v>0.0</v>
       </c>
       <c r="N93" s="2">
-        <v>768.0</v>
+        <v>810.0</v>
       </c>
       <c r="O93" s="2">
-        <v>437.0</v>
+        <v>469.0</v>
       </c>
       <c r="P93" s="2">
-        <v>330.0</v>
+        <v>340.0</v>
       </c>
       <c r="Q93" s="2">
         <v>1.0</v>
       </c>
       <c r="R93" s="2">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
       <c r="S93" s="2">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="T93" s="2">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="U93" s="2">
         <v>0.0</v>
@@ -6956,7 +6956,7 @@
         <v>2.0</v>
       </c>
       <c r="W93" s="2">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
@@ -6988,7 +6988,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" s="2">
-        <v>567.0</v>
+        <v>609.0</v>
       </c>
       <c r="K94" s="2">
         <v>1.0</v>
@@ -7000,13 +7000,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" s="2">
-        <v>567.0</v>
+        <v>609.0</v>
       </c>
       <c r="O94" s="2">
-        <v>251.0</v>
+        <v>278.0</v>
       </c>
       <c r="P94" s="2">
-        <v>316.0</v>
+        <v>331.0</v>
       </c>
       <c r="Q94" s="2">
         <v>0.0</v>
@@ -7059,7 +7059,7 @@
         <v>1421.0</v>
       </c>
       <c r="J95" s="2">
-        <v>1318.0</v>
+        <v>1400.0</v>
       </c>
       <c r="K95" s="2">
         <v>1.0</v>
@@ -7071,13 +7071,13 @@
         <v>0.0</v>
       </c>
       <c r="N95" s="2">
-        <v>1318.0</v>
+        <v>1400.0</v>
       </c>
       <c r="O95" s="2">
-        <v>671.0</v>
+        <v>749.0</v>
       </c>
       <c r="P95" s="2">
-        <v>647.0</v>
+        <v>651.0</v>
       </c>
       <c r="Q95" s="2">
         <v>0.0</v>
@@ -7130,7 +7130,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>787.0</v>
+        <v>921.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7142,13 +7142,13 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>787.0</v>
+        <v>921.0</v>
       </c>
       <c r="O96" s="2">
-        <v>423.0</v>
+        <v>519.0</v>
       </c>
       <c r="P96" s="2">
-        <v>364.0</v>
+        <v>402.0</v>
       </c>
       <c r="Q96" s="2">
         <v>0.0</v>
@@ -7201,7 +7201,7 @@
         <v>1012.0</v>
       </c>
       <c r="J97" s="2">
-        <v>660.0</v>
+        <v>740.0</v>
       </c>
       <c r="K97" s="2">
         <v>1.0</v>
@@ -7213,13 +7213,13 @@
         <v>0.0</v>
       </c>
       <c r="N97" s="2">
-        <v>660.0</v>
+        <v>740.0</v>
       </c>
       <c r="O97" s="2">
-        <v>314.0</v>
+        <v>360.0</v>
       </c>
       <c r="P97" s="2">
-        <v>346.0</v>
+        <v>380.0</v>
       </c>
       <c r="Q97" s="2">
         <v>0.0</v>
@@ -7272,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>431.0</v>
+        <v>595.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7284,19 +7284,19 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>431.0</v>
+        <v>595.0</v>
       </c>
       <c r="O98" s="2">
-        <v>170.0</v>
+        <v>279.0</v>
       </c>
       <c r="P98" s="2">
-        <v>255.0</v>
+        <v>308.0</v>
       </c>
       <c r="Q98" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="R98" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="S98" s="2">
         <v>2.0</v>
@@ -7311,7 +7311,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7343,7 +7343,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" s="2">
-        <v>717.0</v>
+        <v>755.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7355,13 +7355,13 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>717.0</v>
+        <v>755.0</v>
       </c>
       <c r="O99" s="2">
-        <v>365.0</v>
+        <v>389.0</v>
       </c>
       <c r="P99" s="2">
-        <v>352.0</v>
+        <v>366.0</v>
       </c>
       <c r="Q99" s="2">
         <v>0.0</v>
@@ -7414,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>1012.0</v>
+        <v>1075.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7426,16 +7426,16 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>1012.0</v>
+        <v>1075.0</v>
       </c>
       <c r="O100" s="2">
-        <v>415.0</v>
+        <v>470.0</v>
       </c>
       <c r="P100" s="2">
-        <v>597.0</v>
+        <v>604.0</v>
       </c>
       <c r="Q100" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R100" s="2">
         <v>0.0</v>
@@ -7485,7 +7485,7 @@
         <v>1059.0</v>
       </c>
       <c r="J101" s="2">
-        <v>932.0</v>
+        <v>946.0</v>
       </c>
       <c r="K101" s="2">
         <v>1.0</v>
@@ -7497,13 +7497,13 @@
         <v>0.0</v>
       </c>
       <c r="N101" s="2">
-        <v>932.0</v>
+        <v>946.0</v>
       </c>
       <c r="O101" s="2">
-        <v>487.0</v>
+        <v>492.0</v>
       </c>
       <c r="P101" s="2">
-        <v>445.0</v>
+        <v>454.0</v>
       </c>
       <c r="Q101" s="2">
         <v>0.0</v>
@@ -7512,7 +7512,7 @@
         <v>46.0</v>
       </c>
       <c r="S101" s="2">
-        <v>50.0</v>
+        <v>55.0</v>
       </c>
       <c r="T101" s="2">
         <v>2.0</v>
@@ -7524,7 +7524,7 @@
         <v>0.0</v>
       </c>
       <c r="W101" s="2">
-        <v>98.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
@@ -7556,7 +7556,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>852.0</v>
+        <v>922.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7568,22 +7568,22 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>852.0</v>
+        <v>922.0</v>
       </c>
       <c r="O102" s="2">
-        <v>425.0</v>
+        <v>466.0</v>
       </c>
       <c r="P102" s="2">
-        <v>427.0</v>
+        <v>456.0</v>
       </c>
       <c r="Q102" s="2">
         <v>0.0</v>
       </c>
       <c r="R102" s="2">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="S102" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="T102" s="2">
         <v>0.0</v>
@@ -7595,7 +7595,7 @@
         <v>0.0</v>
       </c>
       <c r="W102" s="2">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -7627,7 +7627,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" s="2">
-        <v>451.0</v>
+        <v>504.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7639,19 +7639,19 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>451.0</v>
+        <v>504.0</v>
       </c>
       <c r="O103" s="2">
-        <v>239.0</v>
+        <v>283.0</v>
       </c>
       <c r="P103" s="2">
-        <v>212.0</v>
+        <v>221.0</v>
       </c>
       <c r="Q103" s="2">
         <v>0.0</v>
       </c>
       <c r="R103" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="S103" s="2">
         <v>0.0</v>
@@ -7666,7 +7666,7 @@
         <v>0.0</v>
       </c>
       <c r="W103" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -7769,7 +7769,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" s="2">
-        <v>758.0</v>
+        <v>860.0</v>
       </c>
       <c r="K105" s="2">
         <v>1.0</v>
@@ -7781,22 +7781,22 @@
         <v>0.0</v>
       </c>
       <c r="N105" s="2">
-        <v>758.0</v>
+        <v>860.0</v>
       </c>
       <c r="O105" s="2">
-        <v>397.0</v>
+        <v>490.0</v>
       </c>
       <c r="P105" s="2">
-        <v>361.0</v>
+        <v>370.0</v>
       </c>
       <c r="Q105" s="2">
         <v>0.0</v>
       </c>
       <c r="R105" s="2">
-        <v>34.0</v>
+        <v>40.0</v>
       </c>
       <c r="S105" s="2">
-        <v>79.0</v>
+        <v>106.0</v>
       </c>
       <c r="T105" s="2">
         <v>0.0</v>
@@ -7808,7 +7808,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" s="2">
-        <v>113.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -7840,7 +7840,7 @@
         <v>1098.0</v>
       </c>
       <c r="J106" s="2">
-        <v>760.0</v>
+        <v>870.0</v>
       </c>
       <c r="K106" s="2">
         <v>1.0</v>
@@ -7852,25 +7852,25 @@
         <v>0.0</v>
       </c>
       <c r="N106" s="2">
-        <v>760.0</v>
+        <v>870.0</v>
       </c>
       <c r="O106" s="2">
-        <v>328.0</v>
+        <v>400.0</v>
       </c>
       <c r="P106" s="2">
-        <v>422.0</v>
+        <v>457.0</v>
       </c>
       <c r="Q106" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="R106" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="S106" s="2">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="T106" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="U106" s="2">
         <v>1.0</v>
@@ -7879,7 +7879,7 @@
         <v>0.0</v>
       </c>
       <c r="W106" s="2">
-        <v>102.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
@@ -7911,7 +7911,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" s="2">
-        <v>578.0</v>
+        <v>643.0</v>
       </c>
       <c r="K107" s="2">
         <v>1.0</v>
@@ -7920,16 +7920,16 @@
         <v>1.0</v>
       </c>
       <c r="M107" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="N107" s="2">
-        <v>575.0</v>
+        <v>639.0</v>
       </c>
       <c r="O107" s="2">
-        <v>291.0</v>
+        <v>340.0</v>
       </c>
       <c r="P107" s="2">
-        <v>287.0</v>
+        <v>303.0</v>
       </c>
       <c r="Q107" s="2">
         <v>0.0</v>
@@ -7982,7 +7982,7 @@
         <v>950.0</v>
       </c>
       <c r="J108" s="2">
-        <v>499.0</v>
+        <v>599.0</v>
       </c>
       <c r="K108" s="2">
         <v>1.0</v>
@@ -7994,13 +7994,13 @@
         <v>1.0</v>
       </c>
       <c r="N108" s="2">
-        <v>498.0</v>
+        <v>598.0</v>
       </c>
       <c r="O108" s="2">
-        <v>282.0</v>
+        <v>359.0</v>
       </c>
       <c r="P108" s="2">
-        <v>217.0</v>
+        <v>240.0</v>
       </c>
       <c r="Q108" s="2">
         <v>0.0</v>
@@ -8053,7 +8053,7 @@
         <v>821.0</v>
       </c>
       <c r="J109" s="2">
-        <v>604.0</v>
+        <v>622.0</v>
       </c>
       <c r="K109" s="2">
         <v>1.0</v>
@@ -8065,13 +8065,13 @@
         <v>0.0</v>
       </c>
       <c r="N109" s="2">
-        <v>604.0</v>
+        <v>622.0</v>
       </c>
       <c r="O109" s="2">
-        <v>317.0</v>
+        <v>330.0</v>
       </c>
       <c r="P109" s="2">
-        <v>287.0</v>
+        <v>292.0</v>
       </c>
       <c r="Q109" s="2">
         <v>0.0</v>
@@ -8080,7 +8080,7 @@
         <v>28.0</v>
       </c>
       <c r="S109" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="T109" s="2">
         <v>3.0</v>
@@ -8092,7 +8092,7 @@
         <v>0.0</v>
       </c>
       <c r="W109" s="2">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
@@ -8124,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>436.0</v>
+        <v>492.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8136,22 +8136,22 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>436.0</v>
+        <v>492.0</v>
       </c>
       <c r="O110" s="2">
-        <v>199.0</v>
+        <v>238.0</v>
       </c>
       <c r="P110" s="2">
-        <v>237.0</v>
+        <v>254.0</v>
       </c>
       <c r="Q110" s="2">
         <v>0.0</v>
       </c>
       <c r="R110" s="2">
-        <v>13.0</v>
+        <v>28.0</v>
       </c>
       <c r="S110" s="2">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="T110" s="2">
         <v>0.0</v>
@@ -8163,7 +8163,7 @@
         <v>0.0</v>
       </c>
       <c r="W110" s="2">
-        <v>26.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
@@ -8195,7 +8195,7 @@
         <v>1027.0</v>
       </c>
       <c r="J111" s="2">
-        <v>772.0</v>
+        <v>819.0</v>
       </c>
       <c r="K111" s="2">
         <v>1.0</v>
@@ -8207,16 +8207,16 @@
         <v>0.0</v>
       </c>
       <c r="N111" s="2">
-        <v>772.0</v>
+        <v>819.0</v>
       </c>
       <c r="O111" s="2">
-        <v>343.0</v>
+        <v>385.0</v>
       </c>
       <c r="P111" s="2">
-        <v>426.0</v>
+        <v>429.0</v>
       </c>
       <c r="Q111" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="R111" s="2">
         <v>5.0</v>
@@ -8266,7 +8266,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" s="2">
-        <v>544.0</v>
+        <v>556.0</v>
       </c>
       <c r="K112" s="2">
         <v>1.0</v>
@@ -8278,13 +8278,13 @@
         <v>0.0</v>
       </c>
       <c r="N112" s="2">
-        <v>544.0</v>
+        <v>556.0</v>
       </c>
       <c r="O112" s="2">
-        <v>278.0</v>
+        <v>284.0</v>
       </c>
       <c r="P112" s="2">
-        <v>262.0</v>
+        <v>268.0</v>
       </c>
       <c r="Q112" s="2">
         <v>4.0</v>
@@ -8293,7 +8293,7 @@
         <v>11.0</v>
       </c>
       <c r="S112" s="2">
-        <v>44.0</v>
+        <v>53.0</v>
       </c>
       <c r="T112" s="2">
         <v>1.0</v>
@@ -8305,7 +8305,7 @@
         <v>0.0</v>
       </c>
       <c r="W112" s="2">
-        <v>57.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -8337,7 +8337,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" s="2">
-        <v>570.0</v>
+        <v>638.0</v>
       </c>
       <c r="K113" s="2">
         <v>1.0</v>
@@ -8349,19 +8349,19 @@
         <v>0.0</v>
       </c>
       <c r="N113" s="2">
-        <v>570.0</v>
+        <v>638.0</v>
       </c>
       <c r="O113" s="2">
-        <v>187.0</v>
+        <v>223.0</v>
       </c>
       <c r="P113" s="2">
-        <v>383.0</v>
+        <v>415.0</v>
       </c>
       <c r="Q113" s="2">
         <v>0.0</v>
       </c>
       <c r="R113" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S113" s="2">
         <v>0.0</v>
@@ -8376,7 +8376,7 @@
         <v>0.0</v>
       </c>
       <c r="W113" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
@@ -8408,7 +8408,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>529.0</v>
+        <v>536.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8420,13 +8420,13 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>529.0</v>
+        <v>536.0</v>
       </c>
       <c r="O114" s="2">
-        <v>273.0</v>
+        <v>275.0</v>
       </c>
       <c r="P114" s="2">
-        <v>255.0</v>
+        <v>260.0</v>
       </c>
       <c r="Q114" s="2">
         <v>1.0</v>
@@ -8503,7 +8503,7 @@
         <v>0.0</v>
       </c>
       <c r="R115" s="2">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
       <c r="S115" s="2">
         <v>0.0</v>
@@ -8518,7 +8518,7 @@
         <v>0.0</v>
       </c>
       <c r="W115" s="2">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
@@ -8550,7 +8550,7 @@
         <v>1148.0</v>
       </c>
       <c r="J116" s="2">
-        <v>652.0</v>
+        <v>694.0</v>
       </c>
       <c r="K116" s="2">
         <v>1.0</v>
@@ -8562,16 +8562,16 @@
         <v>1.0</v>
       </c>
       <c r="N116" s="2">
-        <v>651.0</v>
+        <v>693.0</v>
       </c>
       <c r="O116" s="2">
-        <v>63.0</v>
+        <v>69.0</v>
       </c>
       <c r="P116" s="2">
-        <v>279.0</v>
+        <v>296.0</v>
       </c>
       <c r="Q116" s="2">
-        <v>310.0</v>
+        <v>329.0</v>
       </c>
       <c r="R116" s="2">
         <v>0.0</v>
@@ -8621,7 +8621,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>564.0</v>
+        <v>644.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8633,13 +8633,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>563.0</v>
+        <v>643.0</v>
       </c>
       <c r="O117" s="2">
-        <v>275.0</v>
+        <v>315.0</v>
       </c>
       <c r="P117" s="2">
-        <v>289.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q117" s="2">
         <v>0.0</v>
@@ -8692,7 +8692,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>598.0</v>
+        <v>718.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8704,22 +8704,22 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>598.0</v>
+        <v>718.0</v>
       </c>
       <c r="O118" s="2">
-        <v>307.0</v>
+        <v>381.0</v>
       </c>
       <c r="P118" s="2">
-        <v>289.0</v>
+        <v>333.0</v>
       </c>
       <c r="Q118" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R118" s="2">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
       <c r="S118" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="T118" s="2">
         <v>1.0</v>
@@ -8731,7 +8731,7 @@
         <v>2.0</v>
       </c>
       <c r="W118" s="2">
-        <v>42.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
@@ -8763,7 +8763,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>656.0</v>
+        <v>681.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8775,19 +8775,19 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>656.0</v>
+        <v>681.0</v>
       </c>
       <c r="O119" s="2">
-        <v>383.0</v>
+        <v>400.0</v>
       </c>
       <c r="P119" s="2">
-        <v>268.0</v>
+        <v>276.0</v>
       </c>
       <c r="Q119" s="2">
         <v>5.0</v>
       </c>
       <c r="R119" s="2">
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
       <c r="S119" s="2">
         <v>10.0</v>
@@ -8802,7 +8802,7 @@
         <v>0.0</v>
       </c>
       <c r="W119" s="2">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -8834,7 +8834,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>492.0</v>
+        <v>588.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8846,19 +8846,19 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>492.0</v>
+        <v>588.0</v>
       </c>
       <c r="O120" s="2">
-        <v>240.0</v>
+        <v>299.0</v>
       </c>
       <c r="P120" s="2">
-        <v>249.0</v>
+        <v>286.0</v>
       </c>
       <c r="Q120" s="2">
         <v>3.0</v>
       </c>
       <c r="R120" s="2">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="S120" s="2">
         <v>3.0</v>
@@ -8873,7 +8873,7 @@
         <v>0.0</v>
       </c>
       <c r="W120" s="2">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -8905,7 +8905,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>589.0</v>
+        <v>633.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8917,22 +8917,22 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>589.0</v>
+        <v>633.0</v>
       </c>
       <c r="O121" s="2">
-        <v>358.0</v>
+        <v>389.0</v>
       </c>
       <c r="P121" s="2">
-        <v>231.0</v>
+        <v>244.0</v>
       </c>
       <c r="Q121" s="2">
         <v>0.0</v>
       </c>
       <c r="R121" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="S121" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T121" s="2">
         <v>0.0</v>
@@ -8944,7 +8944,7 @@
         <v>0.0</v>
       </c>
       <c r="W121" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -8976,7 +8976,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>529.0</v>
+        <v>575.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8988,13 +8988,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>525.0</v>
+        <v>571.0</v>
       </c>
       <c r="O122" s="2">
-        <v>289.0</v>
+        <v>324.0</v>
       </c>
       <c r="P122" s="2">
-        <v>225.0</v>
+        <v>236.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -9047,7 +9047,7 @@
         <v>623.0</v>
       </c>
       <c r="J123" s="2">
-        <v>541.0</v>
+        <v>571.0</v>
       </c>
       <c r="K123" s="2">
         <v>1.0</v>
@@ -9059,19 +9059,19 @@
         <v>0.0</v>
       </c>
       <c r="N123" s="2">
-        <v>541.0</v>
+        <v>571.0</v>
       </c>
       <c r="O123" s="2">
-        <v>275.0</v>
+        <v>300.0</v>
       </c>
       <c r="P123" s="2">
-        <v>249.0</v>
+        <v>263.0</v>
       </c>
       <c r="Q123" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="R123" s="2">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="S123" s="2">
         <v>6.0</v>
@@ -9086,7 +9086,7 @@
         <v>0.0</v>
       </c>
       <c r="W123" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
@@ -9189,7 +9189,7 @@
         <v>1432.0</v>
       </c>
       <c r="J125" s="2">
-        <v>1188.0</v>
+        <v>1214.0</v>
       </c>
       <c r="K125" s="2">
         <v>1.0</v>
@@ -9201,34 +9201,34 @@
         <v>0.0</v>
       </c>
       <c r="N125" s="2">
-        <v>1188.0</v>
+        <v>1214.0</v>
       </c>
       <c r="O125" s="2">
-        <v>539.0</v>
+        <v>552.0</v>
       </c>
       <c r="P125" s="2">
-        <v>589.0</v>
+        <v>596.0</v>
       </c>
       <c r="Q125" s="2">
-        <v>60.0</v>
+        <v>66.0</v>
       </c>
       <c r="R125" s="2">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
       <c r="S125" s="2">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="T125" s="2">
         <v>0.0</v>
       </c>
       <c r="U125" s="2">
-        <v>12.0</v>
+        <v>131.0</v>
       </c>
       <c r="V125" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="W125" s="2">
-        <v>80.0</v>
+        <v>218.0</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
@@ -9260,7 +9260,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" s="2">
-        <v>771.0</v>
+        <v>833.0</v>
       </c>
       <c r="K126" s="2">
         <v>1.0</v>
@@ -9272,22 +9272,22 @@
         <v>0.0</v>
       </c>
       <c r="N126" s="2">
-        <v>771.0</v>
+        <v>833.0</v>
       </c>
       <c r="O126" s="2">
-        <v>407.0</v>
+        <v>433.0</v>
       </c>
       <c r="P126" s="2">
-        <v>362.0</v>
+        <v>383.0</v>
       </c>
       <c r="Q126" s="2">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="R126" s="2">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="S126" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="T126" s="2">
         <v>0.0</v>
@@ -9299,7 +9299,7 @@
         <v>0.0</v>
       </c>
       <c r="W126" s="2">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
@@ -9331,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>763.0</v>
+        <v>818.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9343,13 +9343,13 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>763.0</v>
+        <v>818.0</v>
       </c>
       <c r="O127" s="2">
-        <v>490.0</v>
+        <v>524.0</v>
       </c>
       <c r="P127" s="2">
-        <v>273.0</v>
+        <v>294.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
@@ -9402,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>837.0</v>
+        <v>938.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9414,34 +9414,34 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>837.0</v>
+        <v>938.0</v>
       </c>
       <c r="O128" s="2">
-        <v>453.0</v>
+        <v>522.0</v>
       </c>
       <c r="P128" s="2">
-        <v>382.0</v>
+        <v>414.0</v>
       </c>
       <c r="Q128" s="2">
         <v>2.0</v>
       </c>
       <c r="R128" s="2">
-        <v>15.0</v>
+        <v>22.0</v>
       </c>
       <c r="S128" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="T128" s="2">
         <v>0.0</v>
       </c>
       <c r="U128" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="V128" s="2">
         <v>0.0</v>
       </c>
       <c r="W128" s="2">
-        <v>17.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
@@ -9473,7 +9473,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" s="2">
-        <v>521.0</v>
+        <v>595.0</v>
       </c>
       <c r="K129" s="2">
         <v>1.0</v>
@@ -9485,22 +9485,22 @@
         <v>0.0</v>
       </c>
       <c r="N129" s="2">
-        <v>521.0</v>
+        <v>595.0</v>
       </c>
       <c r="O129" s="2">
-        <v>315.0</v>
+        <v>384.0</v>
       </c>
       <c r="P129" s="2">
-        <v>205.0</v>
+        <v>210.0</v>
       </c>
       <c r="Q129" s="2">
         <v>1.0</v>
       </c>
       <c r="R129" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S129" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T129" s="2">
         <v>0.0</v>
@@ -9512,7 +9512,7 @@
         <v>0.0</v>
       </c>
       <c r="W129" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
@@ -9544,7 +9544,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" s="2">
-        <v>579.0</v>
+        <v>603.0</v>
       </c>
       <c r="K130" s="2">
         <v>1.0</v>
@@ -9556,34 +9556,34 @@
         <v>2.0</v>
       </c>
       <c r="N130" s="2">
-        <v>577.0</v>
+        <v>601.0</v>
       </c>
       <c r="O130" s="2">
-        <v>374.0</v>
+        <v>393.0</v>
       </c>
       <c r="P130" s="2">
-        <v>175.0</v>
+        <v>179.0</v>
       </c>
       <c r="Q130" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="R130" s="2">
-        <v>12.0</v>
+        <v>27.0</v>
       </c>
       <c r="S130" s="2">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="T130" s="2">
         <v>3.0</v>
       </c>
       <c r="U130" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="V130" s="2">
         <v>0.0</v>
       </c>
       <c r="W130" s="2">
-        <v>15.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
@@ -9686,7 +9686,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" s="2">
-        <v>536.0</v>
+        <v>640.0</v>
       </c>
       <c r="K132" s="2">
         <v>1.0</v>
@@ -9698,34 +9698,34 @@
         <v>4.0</v>
       </c>
       <c r="N132" s="2">
-        <v>532.0</v>
+        <v>636.0</v>
       </c>
       <c r="O132" s="2">
-        <v>227.0</v>
+        <v>287.0</v>
       </c>
       <c r="P132" s="2">
-        <v>300.0</v>
+        <v>340.0</v>
       </c>
       <c r="Q132" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="R132" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S132" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T132" s="2">
         <v>0.0</v>
       </c>
       <c r="U132" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V132" s="2">
         <v>0.0</v>
       </c>
       <c r="W132" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
@@ -9757,7 +9757,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" s="2">
-        <v>738.0</v>
+        <v>861.0</v>
       </c>
       <c r="K133" s="2">
         <v>1.0</v>
@@ -9769,16 +9769,16 @@
         <v>0.0</v>
       </c>
       <c r="N133" s="2">
-        <v>738.0</v>
+        <v>861.0</v>
       </c>
       <c r="O133" s="2">
+        <v>454.0</v>
+      </c>
+      <c r="P133" s="2">
         <v>394.0</v>
       </c>
-      <c r="P133" s="2">
-        <v>333.0</v>
-      </c>
       <c r="Q133" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="R133" s="2">
         <v>0.0</v>
@@ -9828,7 +9828,7 @@
         <v>1343.0</v>
       </c>
       <c r="J134" s="2">
-        <v>1101.0</v>
+        <v>1219.0</v>
       </c>
       <c r="K134" s="2">
         <v>1.0</v>
@@ -9840,34 +9840,34 @@
         <v>1.0</v>
       </c>
       <c r="N134" s="2">
-        <v>1100.0</v>
+        <v>1218.0</v>
       </c>
       <c r="O134" s="2">
-        <v>710.0</v>
+        <v>748.0</v>
       </c>
       <c r="P134" s="2">
-        <v>383.0</v>
+        <v>399.0</v>
       </c>
       <c r="Q134" s="2">
-        <v>8.0</v>
+        <v>72.0</v>
       </c>
       <c r="R134" s="2">
-        <v>43.0</v>
+        <v>46.0</v>
       </c>
       <c r="S134" s="2">
-        <v>56.0</v>
+        <v>62.0</v>
       </c>
       <c r="T134" s="2">
         <v>0.0</v>
       </c>
       <c r="U134" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="V134" s="2">
         <v>2.0</v>
       </c>
       <c r="W134" s="2">
-        <v>113.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
@@ -9899,7 +9899,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" s="2">
-        <v>772.0</v>
+        <v>878.0</v>
       </c>
       <c r="K135" s="2">
         <v>1.0</v>
@@ -9911,19 +9911,19 @@
         <v>1.0</v>
       </c>
       <c r="N135" s="2">
-        <v>771.0</v>
+        <v>877.0</v>
       </c>
       <c r="O135" s="2">
-        <v>383.0</v>
+        <v>431.0</v>
       </c>
       <c r="P135" s="2">
-        <v>307.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q135" s="2">
         <v>82.0</v>
       </c>
       <c r="R135" s="2">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="S135" s="2">
         <v>1.0</v>
@@ -9938,7 +9938,7 @@
         <v>0.0</v>
       </c>
       <c r="W135" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
@@ -9970,7 +9970,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" s="2">
-        <v>623.0</v>
+        <v>804.0</v>
       </c>
       <c r="K136" s="2">
         <v>1.0</v>
@@ -9982,16 +9982,16 @@
         <v>0.0</v>
       </c>
       <c r="N136" s="2">
-        <v>623.0</v>
+        <v>804.0</v>
       </c>
       <c r="O136" s="2">
-        <v>336.0</v>
+        <v>440.0</v>
       </c>
       <c r="P136" s="2">
-        <v>277.0</v>
+        <v>353.0</v>
       </c>
       <c r="Q136" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R136" s="2">
         <v>16.0</v>
@@ -10006,10 +10006,10 @@
         <v>4.0</v>
       </c>
       <c r="V136" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="W136" s="2">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
@@ -10041,7 +10041,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>524.0</v>
+        <v>584.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10053,22 +10053,22 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>524.0</v>
+        <v>584.0</v>
       </c>
       <c r="O137" s="2">
-        <v>221.0</v>
+        <v>268.0</v>
       </c>
       <c r="P137" s="2">
-        <v>289.0</v>
+        <v>302.0</v>
       </c>
       <c r="Q137" s="2">
         <v>14.0</v>
       </c>
       <c r="R137" s="2">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="S137" s="2">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="T137" s="2">
         <v>0.0</v>
@@ -10080,7 +10080,7 @@
         <v>0.0</v>
       </c>
       <c r="W137" s="2">
-        <v>42.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
@@ -10112,7 +10112,7 @@
         <v>1169.0</v>
       </c>
       <c r="J138" s="2">
-        <v>629.0</v>
+        <v>669.0</v>
       </c>
       <c r="K138" s="2">
         <v>1.0</v>
@@ -10124,13 +10124,13 @@
         <v>0.0</v>
       </c>
       <c r="N138" s="2">
-        <v>629.0</v>
+        <v>669.0</v>
       </c>
       <c r="O138" s="2">
-        <v>323.0</v>
+        <v>357.0</v>
       </c>
       <c r="P138" s="2">
-        <v>282.0</v>
+        <v>288.0</v>
       </c>
       <c r="Q138" s="2">
         <v>24.0</v>
@@ -10183,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>754.0</v>
+        <v>822.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10195,22 +10195,22 @@
         <v>0.0</v>
       </c>
       <c r="N139" s="2">
-        <v>754.0</v>
+        <v>822.0</v>
       </c>
       <c r="O139" s="2">
-        <v>452.0</v>
+        <v>508.0</v>
       </c>
       <c r="P139" s="2">
-        <v>281.0</v>
+        <v>293.0</v>
       </c>
       <c r="Q139" s="2">
         <v>21.0</v>
       </c>
       <c r="R139" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="S139" s="2">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="T139" s="2">
         <v>0.0</v>
@@ -10222,7 +10222,7 @@
         <v>0.0</v>
       </c>
       <c r="W139" s="2">
-        <v>54.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -10254,7 +10254,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>627.0</v>
+        <v>647.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10266,19 +10266,19 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>627.0</v>
+        <v>647.0</v>
       </c>
       <c r="O140" s="2">
-        <v>310.0</v>
+        <v>324.0</v>
       </c>
       <c r="P140" s="2">
-        <v>316.0</v>
+        <v>322.0</v>
       </c>
       <c r="Q140" s="2">
         <v>1.0</v>
       </c>
       <c r="R140" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S140" s="2">
         <v>8.0</v>
@@ -10293,7 +10293,7 @@
         <v>0.0</v>
       </c>
       <c r="W140" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -10325,7 +10325,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>649.0</v>
+        <v>654.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10337,10 +10337,10 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>648.0</v>
+        <v>653.0</v>
       </c>
       <c r="O141" s="2">
-        <v>378.0</v>
+        <v>383.0</v>
       </c>
       <c r="P141" s="2">
         <v>271.0</v>
@@ -10396,7 +10396,7 @@
         <v>1047.0</v>
       </c>
       <c r="J142" s="2">
-        <v>876.0</v>
+        <v>897.0</v>
       </c>
       <c r="K142" s="2">
         <v>1.0</v>
@@ -10408,10 +10408,10 @@
         <v>0.0</v>
       </c>
       <c r="N142" s="2">
-        <v>876.0</v>
+        <v>897.0</v>
       </c>
       <c r="O142" s="2">
-        <v>485.0</v>
+        <v>506.0</v>
       </c>
       <c r="P142" s="2">
         <v>391.0</v>
@@ -10467,7 +10467,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>604.0</v>
+        <v>735.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10479,13 +10479,13 @@
         <v>1.0</v>
       </c>
       <c r="N143" s="2">
-        <v>603.0</v>
+        <v>734.0</v>
       </c>
       <c r="O143" s="2">
-        <v>371.0</v>
+        <v>442.0</v>
       </c>
       <c r="P143" s="2">
-        <v>233.0</v>
+        <v>293.0</v>
       </c>
       <c r="Q143" s="2">
         <v>0.0</v>
@@ -10538,7 +10538,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>723.0</v>
+        <v>751.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10550,13 +10550,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>723.0</v>
+        <v>751.0</v>
       </c>
       <c r="O144" s="2">
-        <v>375.0</v>
+        <v>398.0</v>
       </c>
       <c r="P144" s="2">
-        <v>348.0</v>
+        <v>353.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
@@ -10609,7 +10609,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" s="2">
-        <v>579.0</v>
+        <v>610.0</v>
       </c>
       <c r="K145" s="2">
         <v>1.0</v>
@@ -10621,22 +10621,22 @@
         <v>0.0</v>
       </c>
       <c r="N145" s="2">
-        <v>579.0</v>
+        <v>610.0</v>
       </c>
       <c r="O145" s="2">
-        <v>232.0</v>
+        <v>243.0</v>
       </c>
       <c r="P145" s="2">
-        <v>328.0</v>
+        <v>344.0</v>
       </c>
       <c r="Q145" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="R145" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="S145" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="T145" s="2">
         <v>1.0</v>
@@ -10648,7 +10648,7 @@
         <v>1.0</v>
       </c>
       <c r="W145" s="2">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
@@ -10680,7 +10680,7 @@
         <v>863.0</v>
       </c>
       <c r="J146" s="2">
-        <v>367.0</v>
+        <v>434.0</v>
       </c>
       <c r="K146" s="2">
         <v>1.0</v>
@@ -10692,22 +10692,22 @@
         <v>2.0</v>
       </c>
       <c r="N146" s="2">
-        <v>365.0</v>
+        <v>432.0</v>
       </c>
       <c r="O146" s="2">
-        <v>161.0</v>
+        <v>192.0</v>
       </c>
       <c r="P146" s="2">
-        <v>206.0</v>
+        <v>242.0</v>
       </c>
       <c r="Q146" s="2">
         <v>0.0</v>
       </c>
       <c r="R146" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="S146" s="2">
-        <v>2.0</v>
+        <v>24.0</v>
       </c>
       <c r="T146" s="2">
         <v>0.0</v>
@@ -10719,7 +10719,7 @@
         <v>0.0</v>
       </c>
       <c r="W146" s="2">
-        <v>13.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
@@ -10751,7 +10751,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>329.0</v>
+        <v>391.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10763,13 +10763,13 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>329.0</v>
+        <v>391.0</v>
       </c>
       <c r="O147" s="2">
-        <v>149.0</v>
+        <v>178.0</v>
       </c>
       <c r="P147" s="2">
-        <v>161.0</v>
+        <v>194.0</v>
       </c>
       <c r="Q147" s="2">
         <v>19.0</v>
@@ -10893,7 +10893,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>492.0</v>
+        <v>548.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10905,19 +10905,19 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>492.0</v>
+        <v>548.0</v>
       </c>
       <c r="O149" s="2">
-        <v>280.0</v>
+        <v>323.0</v>
       </c>
       <c r="P149" s="2">
-        <v>208.0</v>
+        <v>221.0</v>
       </c>
       <c r="Q149" s="2">
         <v>4.0</v>
       </c>
       <c r="R149" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S149" s="2">
         <v>0.0</v>
@@ -10932,7 +10932,7 @@
         <v>0.0</v>
       </c>
       <c r="W149" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
@@ -11035,7 +11035,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" s="2">
-        <v>401.0</v>
+        <v>451.0</v>
       </c>
       <c r="K151" s="2">
         <v>1.0</v>
@@ -11047,13 +11047,13 @@
         <v>0.0</v>
       </c>
       <c r="N151" s="2">
-        <v>401.0</v>
+        <v>451.0</v>
       </c>
       <c r="O151" s="2">
-        <v>199.0</v>
+        <v>221.0</v>
       </c>
       <c r="P151" s="2">
-        <v>202.0</v>
+        <v>230.0</v>
       </c>
       <c r="Q151" s="2">
         <v>0.0</v>
@@ -11106,7 +11106,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" s="2">
-        <v>553.0</v>
+        <v>588.0</v>
       </c>
       <c r="K152" s="2">
         <v>1.0</v>
@@ -11118,13 +11118,13 @@
         <v>1.0</v>
       </c>
       <c r="N152" s="2">
-        <v>552.0</v>
+        <v>587.0</v>
       </c>
       <c r="O152" s="2">
-        <v>269.0</v>
+        <v>287.0</v>
       </c>
       <c r="P152" s="2">
-        <v>284.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q152" s="2">
         <v>0.0</v>
@@ -11133,7 +11133,7 @@
         <v>9.0</v>
       </c>
       <c r="S152" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T152" s="2">
         <v>0.0</v>
@@ -11145,7 +11145,7 @@
         <v>0.0</v>
       </c>
       <c r="W152" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
@@ -11177,7 +11177,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>768.0</v>
+        <v>791.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11189,19 +11189,19 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>768.0</v>
+        <v>791.0</v>
       </c>
       <c r="O153" s="2">
-        <v>374.0</v>
+        <v>387.0</v>
       </c>
       <c r="P153" s="2">
-        <v>394.0</v>
+        <v>403.0</v>
       </c>
       <c r="Q153" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R153" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S153" s="2">
         <v>0.0</v>
@@ -11216,7 +11216,7 @@
         <v>0.0</v>
       </c>
       <c r="W153" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
@@ -11248,7 +11248,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" s="2">
-        <v>565.0</v>
+        <v>574.0</v>
       </c>
       <c r="K154" s="2">
         <v>1.0</v>
@@ -11260,16 +11260,16 @@
         <v>0.0</v>
       </c>
       <c r="N154" s="2">
-        <v>565.0</v>
+        <v>574.0</v>
       </c>
       <c r="O154" s="2">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
       <c r="P154" s="2">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="Q154" s="2">
-        <v>222.0</v>
+        <v>225.0</v>
       </c>
       <c r="R154" s="2">
         <v>0.0</v>
@@ -11319,7 +11319,7 @@
         <v>1180.0</v>
       </c>
       <c r="J155" s="2">
-        <v>752.0</v>
+        <v>857.0</v>
       </c>
       <c r="K155" s="2">
         <v>1.0</v>
@@ -11331,25 +11331,25 @@
         <v>0.0</v>
       </c>
       <c r="N155" s="2">
-        <v>752.0</v>
+        <v>857.0</v>
       </c>
       <c r="O155" s="2">
-        <v>366.0</v>
+        <v>413.0</v>
       </c>
       <c r="P155" s="2">
-        <v>386.0</v>
+        <v>444.0</v>
       </c>
       <c r="Q155" s="2">
         <v>0.0</v>
       </c>
       <c r="R155" s="2">
-        <v>11.0</v>
+        <v>28.0</v>
       </c>
       <c r="S155" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T155" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U155" s="2">
         <v>0.0</v>
@@ -11358,7 +11358,7 @@
         <v>0.0</v>
       </c>
       <c r="W155" s="2">
-        <v>12.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
@@ -11390,7 +11390,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" s="2">
-        <v>662.0</v>
+        <v>703.0</v>
       </c>
       <c r="K156" s="2">
         <v>1.0</v>
@@ -11402,13 +11402,13 @@
         <v>0.0</v>
       </c>
       <c r="N156" s="2">
-        <v>662.0</v>
+        <v>703.0</v>
       </c>
       <c r="O156" s="2">
-        <v>219.0</v>
+        <v>241.0</v>
       </c>
       <c r="P156" s="2">
-        <v>442.0</v>
+        <v>461.0</v>
       </c>
       <c r="Q156" s="2">
         <v>1.0</v>
@@ -11461,7 +11461,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" s="2">
-        <v>754.0</v>
+        <v>800.0</v>
       </c>
       <c r="K157" s="2">
         <v>1.0</v>
@@ -11473,13 +11473,13 @@
         <v>4.0</v>
       </c>
       <c r="N157" s="2">
-        <v>750.0</v>
+        <v>796.0</v>
       </c>
       <c r="O157" s="2">
-        <v>257.0</v>
+        <v>299.0</v>
       </c>
       <c r="P157" s="2">
-        <v>497.0</v>
+        <v>501.0</v>
       </c>
       <c r="Q157" s="2">
         <v>0.0</v>
@@ -11532,7 +11532,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>691.0</v>
+        <v>711.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11544,13 +11544,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>691.0</v>
+        <v>711.0</v>
       </c>
       <c r="O158" s="2">
-        <v>315.0</v>
+        <v>324.0</v>
       </c>
       <c r="P158" s="2">
-        <v>376.0</v>
+        <v>387.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
@@ -11603,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>734.0</v>
+        <v>802.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11615,22 +11615,22 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>733.0</v>
+        <v>801.0</v>
       </c>
       <c r="O159" s="2">
-        <v>423.0</v>
+        <v>450.0</v>
       </c>
       <c r="P159" s="2">
-        <v>311.0</v>
+        <v>352.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
       </c>
       <c r="R159" s="2">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="S159" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T159" s="2">
         <v>0.0</v>
@@ -11642,7 +11642,7 @@
         <v>0.0</v>
       </c>
       <c r="W159" s="2">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
@@ -11674,7 +11674,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" s="2">
-        <v>835.0</v>
+        <v>940.0</v>
       </c>
       <c r="K160" s="2">
         <v>1.0</v>
@@ -11686,13 +11686,13 @@
         <v>0.0</v>
       </c>
       <c r="N160" s="2">
-        <v>835.0</v>
+        <v>940.0</v>
       </c>
       <c r="O160" s="2">
-        <v>413.0</v>
+        <v>470.0</v>
       </c>
       <c r="P160" s="2">
-        <v>422.0</v>
+        <v>470.0</v>
       </c>
       <c r="Q160" s="2">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>868.0</v>
+        <v>899.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11757,13 +11757,13 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>868.0</v>
+        <v>899.0</v>
       </c>
       <c r="O161" s="2">
-        <v>455.0</v>
+        <v>475.0</v>
       </c>
       <c r="P161" s="2">
-        <v>405.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q161" s="2">
         <v>8.0</v>
@@ -11816,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>737.0</v>
+        <v>789.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11828,16 +11828,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>736.0</v>
+        <v>788.0</v>
       </c>
       <c r="O162" s="2">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
       <c r="P162" s="2">
-        <v>181.0</v>
+        <v>184.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>543.0</v>
+        <v>583.0</v>
       </c>
       <c r="R162" s="2">
         <v>0.0</v>
@@ -11887,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>696.0</v>
+        <v>701.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11899,19 +11899,19 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>696.0</v>
+        <v>701.0</v>
       </c>
       <c r="O163" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="P163" s="2">
-        <v>310.0</v>
+        <v>313.0</v>
       </c>
       <c r="Q163" s="2">
         <v>376.0</v>
       </c>
       <c r="R163" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S163" s="2">
         <v>4.0</v>
@@ -11926,7 +11926,7 @@
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -11958,7 +11958,7 @@
         <v>1054.0</v>
       </c>
       <c r="J164" s="2">
-        <v>685.0</v>
+        <v>709.0</v>
       </c>
       <c r="K164" s="2">
         <v>1.0</v>
@@ -11970,19 +11970,19 @@
         <v>1.0</v>
       </c>
       <c r="N164" s="2">
-        <v>684.0</v>
+        <v>708.0</v>
       </c>
       <c r="O164" s="2">
-        <v>19.0</v>
+        <v>25.0</v>
       </c>
       <c r="P164" s="2">
-        <v>297.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q164" s="2">
-        <v>369.0</v>
+        <v>377.0</v>
       </c>
       <c r="R164" s="2">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
       <c r="S164" s="2">
         <v>0.0</v>
@@ -11997,7 +11997,7 @@
         <v>0.0</v>
       </c>
       <c r="W164" s="2">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
@@ -12100,7 +12100,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>570.0</v>
+        <v>619.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12112,13 +12112,13 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>570.0</v>
+        <v>619.0</v>
       </c>
       <c r="O166" s="2">
-        <v>312.0</v>
+        <v>340.0</v>
       </c>
       <c r="P166" s="2">
-        <v>258.0</v>
+        <v>279.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
@@ -12171,7 +12171,7 @@
         <v>667.0</v>
       </c>
       <c r="J167" s="2">
-        <v>563.0</v>
+        <v>621.0</v>
       </c>
       <c r="K167" s="2">
         <v>1.0</v>
@@ -12183,25 +12183,25 @@
         <v>0.0</v>
       </c>
       <c r="N167" s="2">
-        <v>563.0</v>
+        <v>621.0</v>
       </c>
       <c r="O167" s="2">
-        <v>280.0</v>
+        <v>315.0</v>
       </c>
       <c r="P167" s="2">
-        <v>282.0</v>
+        <v>297.0</v>
       </c>
       <c r="Q167" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="R167" s="2">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
       <c r="S167" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="T167" s="2">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="U167" s="2">
         <v>0.0</v>
@@ -12210,7 +12210,7 @@
         <v>0.0</v>
       </c>
       <c r="W167" s="2">
-        <v>32.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
@@ -12242,7 +12242,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" s="2">
-        <v>522.0</v>
+        <v>666.0</v>
       </c>
       <c r="K168" s="2">
         <v>1.0</v>
@@ -12254,13 +12254,13 @@
         <v>0.0</v>
       </c>
       <c r="N168" s="2">
-        <v>522.0</v>
+        <v>666.0</v>
       </c>
       <c r="O168" s="2">
-        <v>156.0</v>
+        <v>227.0</v>
       </c>
       <c r="P168" s="2">
-        <v>278.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q168" s="2">
         <v>88.0</v>
@@ -12313,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>388.0</v>
+        <v>419.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12325,10 +12325,10 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>388.0</v>
+        <v>419.0</v>
       </c>
       <c r="O169" s="2">
-        <v>179.0</v>
+        <v>210.0</v>
       </c>
       <c r="P169" s="2">
         <v>201.0</v>
@@ -12455,7 +12455,7 @@
         <v>576.0</v>
       </c>
       <c r="J171" s="2">
-        <v>409.0</v>
+        <v>414.0</v>
       </c>
       <c r="K171" s="2">
         <v>1.0</v>
@@ -12467,10 +12467,10 @@
         <v>0.0</v>
       </c>
       <c r="N171" s="2">
-        <v>409.0</v>
+        <v>414.0</v>
       </c>
       <c r="O171" s="2">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="P171" s="2">
         <v>182.0</v>
@@ -12482,7 +12482,7 @@
         <v>0.0</v>
       </c>
       <c r="S171" s="2">
-        <v>1.0</v>
+        <v>37.0</v>
       </c>
       <c r="T171" s="2">
         <v>0.0</v>
@@ -12494,7 +12494,7 @@
         <v>0.0</v>
       </c>
       <c r="W171" s="2">
-        <v>1.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
@@ -12597,7 +12597,7 @@
         <v>1266.0</v>
       </c>
       <c r="J173" s="2">
-        <v>923.0</v>
+        <v>926.0</v>
       </c>
       <c r="K173" s="2">
         <v>1.0</v>
@@ -12609,10 +12609,10 @@
         <v>0.0</v>
       </c>
       <c r="N173" s="2">
-        <v>923.0</v>
+        <v>926.0</v>
       </c>
       <c r="O173" s="2">
-        <v>503.0</v>
+        <v>506.0</v>
       </c>
       <c r="P173" s="2">
         <v>420.0</v>
@@ -12621,13 +12621,13 @@
         <v>0.0</v>
       </c>
       <c r="R173" s="2">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="S173" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="T173" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U173" s="2">
         <v>0.0</v>
@@ -12636,7 +12636,7 @@
         <v>0.0</v>
       </c>
       <c r="W173" s="2">
-        <v>7.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
@@ -12668,7 +12668,7 @@
         <v>1280.0</v>
       </c>
       <c r="J174" s="2">
-        <v>881.0</v>
+        <v>931.0</v>
       </c>
       <c r="K174" s="2">
         <v>1.0</v>
@@ -12680,13 +12680,13 @@
         <v>0.0</v>
       </c>
       <c r="N174" s="2">
-        <v>881.0</v>
+        <v>931.0</v>
       </c>
       <c r="O174" s="2">
-        <v>440.0</v>
+        <v>457.0</v>
       </c>
       <c r="P174" s="2">
-        <v>441.0</v>
+        <v>474.0</v>
       </c>
       <c r="Q174" s="2">
         <v>0.0</v>
@@ -12810,7 +12810,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>475.0</v>
+        <v>502.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12822,16 +12822,16 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>475.0</v>
+        <v>502.0</v>
       </c>
       <c r="O176" s="2">
-        <v>193.0</v>
+        <v>206.0</v>
       </c>
       <c r="P176" s="2">
-        <v>282.0</v>
+        <v>295.0</v>
       </c>
       <c r="Q176" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R176" s="2">
         <v>61.0</v>
@@ -12843,13 +12843,13 @@
         <v>0.0</v>
       </c>
       <c r="U176" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="V176" s="2">
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -12881,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>422.0</v>
+        <v>469.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12893,13 +12893,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>422.0</v>
+        <v>469.0</v>
       </c>
       <c r="O177" s="2">
-        <v>207.0</v>
+        <v>245.0</v>
       </c>
       <c r="P177" s="2">
-        <v>215.0</v>
+        <v>224.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -12952,7 +12952,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>331.0</v>
+        <v>408.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12964,13 +12964,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>331.0</v>
+        <v>408.0</v>
       </c>
       <c r="O178" s="2">
-        <v>152.0</v>
+        <v>174.0</v>
       </c>
       <c r="P178" s="2">
-        <v>178.0</v>
+        <v>233.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
@@ -12982,16 +12982,16 @@
         <v>1.0</v>
       </c>
       <c r="T178" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U178" s="2">
-        <v>47.0</v>
+        <v>51.0</v>
       </c>
       <c r="V178" s="2">
         <v>0.0</v>
       </c>
       <c r="W178" s="2">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -13023,7 +13023,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>541.0</v>
+        <v>602.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13035,19 +13035,19 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>541.0</v>
+        <v>602.0</v>
       </c>
       <c r="O179" s="2">
-        <v>329.0</v>
+        <v>367.0</v>
       </c>
       <c r="P179" s="2">
-        <v>211.0</v>
+        <v>234.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
       <c r="S179" s="2">
         <v>7.0</v>
@@ -13062,7 +13062,7 @@
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -13094,7 +13094,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>375.0</v>
+        <v>396.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13106,13 +13106,13 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>375.0</v>
+        <v>396.0</v>
       </c>
       <c r="O180" s="2">
-        <v>198.0</v>
+        <v>209.0</v>
       </c>
       <c r="P180" s="2">
-        <v>177.0</v>
+        <v>187.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
@@ -13189,22 +13189,22 @@
         <v>0.0</v>
       </c>
       <c r="R181" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="S181" s="2">
-        <v>13.0</v>
+        <v>30.0</v>
       </c>
       <c r="T181" s="2">
         <v>0.0</v>
       </c>
       <c r="U181" s="2">
-        <v>90.0</v>
+        <v>109.0</v>
       </c>
       <c r="V181" s="2">
         <v>0.0</v>
       </c>
       <c r="W181" s="2">
-        <v>115.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -13236,7 +13236,7 @@
         <v>753.0</v>
       </c>
       <c r="J182" s="2">
-        <v>586.0</v>
+        <v>666.0</v>
       </c>
       <c r="K182" s="2">
         <v>1.0</v>
@@ -13248,34 +13248,34 @@
         <v>0.0</v>
       </c>
       <c r="N182" s="2">
-        <v>586.0</v>
+        <v>666.0</v>
       </c>
       <c r="O182" s="2">
-        <v>266.0</v>
+        <v>301.0</v>
       </c>
       <c r="P182" s="2">
-        <v>319.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q182" s="2">
         <v>1.0</v>
       </c>
       <c r="R182" s="2">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="S182" s="2">
-        <v>38.0</v>
+        <v>44.0</v>
       </c>
       <c r="T182" s="2">
         <v>6.0</v>
       </c>
       <c r="U182" s="2">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
       <c r="V182" s="2">
         <v>0.0</v>
       </c>
       <c r="W182" s="2">
-        <v>67.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
@@ -13307,7 +13307,7 @@
         <v>996.0</v>
       </c>
       <c r="J183" s="2">
-        <v>920.0</v>
+        <v>941.0</v>
       </c>
       <c r="K183" s="2">
         <v>1.0</v>
@@ -13319,22 +13319,22 @@
         <v>0.0</v>
       </c>
       <c r="N183" s="2">
-        <v>920.0</v>
+        <v>941.0</v>
       </c>
       <c r="O183" s="2">
-        <v>428.0</v>
+        <v>434.0</v>
       </c>
       <c r="P183" s="2">
-        <v>492.0</v>
+        <v>494.0</v>
       </c>
       <c r="Q183" s="2">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="R183" s="2">
         <v>26.0</v>
       </c>
       <c r="S183" s="2">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="T183" s="2">
         <v>0.0</v>
@@ -13346,7 +13346,7 @@
         <v>1.0</v>
       </c>
       <c r="W183" s="2">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
@@ -13378,7 +13378,7 @@
         <v>899.0</v>
       </c>
       <c r="J184" s="2">
-        <v>373.0</v>
+        <v>435.0</v>
       </c>
       <c r="K184" s="2">
         <v>1.0</v>
@@ -13390,34 +13390,34 @@
         <v>1.0</v>
       </c>
       <c r="N184" s="2">
-        <v>372.0</v>
+        <v>434.0</v>
       </c>
       <c r="O184" s="2">
-        <v>181.0</v>
+        <v>209.0</v>
       </c>
       <c r="P184" s="2">
-        <v>191.0</v>
+        <v>225.0</v>
       </c>
       <c r="Q184" s="2">
         <v>1.0</v>
       </c>
       <c r="R184" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="S184" s="2">
         <v>3.0</v>
       </c>
       <c r="T184" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U184" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V184" s="2">
         <v>0.0</v>
       </c>
       <c r="W184" s="2">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
@@ -13449,7 +13449,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>666.0</v>
+        <v>685.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13461,13 +13461,13 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>666.0</v>
+        <v>685.0</v>
       </c>
       <c r="O185" s="2">
-        <v>350.0</v>
+        <v>362.0</v>
       </c>
       <c r="P185" s="2">
-        <v>316.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q185" s="2">
         <v>0.0</v>
@@ -13520,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>677.0</v>
+        <v>704.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13532,19 +13532,19 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>677.0</v>
+        <v>704.0</v>
       </c>
       <c r="O186" s="2">
-        <v>118.0</v>
+        <v>143.0</v>
       </c>
       <c r="P186" s="2">
         <v>307.0</v>
       </c>
       <c r="Q186" s="2">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
       <c r="R186" s="2">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="S186" s="2">
         <v>0.0</v>
@@ -13559,7 +13559,7 @@
         <v>0.0</v>
       </c>
       <c r="W186" s="2">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1">
@@ -13591,7 +13591,7 @@
         <v>990.0</v>
       </c>
       <c r="J187" s="2">
-        <v>679.0</v>
+        <v>751.0</v>
       </c>
       <c r="K187" s="2">
         <v>1.0</v>
@@ -13603,13 +13603,13 @@
         <v>0.0</v>
       </c>
       <c r="N187" s="2">
-        <v>679.0</v>
+        <v>751.0</v>
       </c>
       <c r="O187" s="2">
-        <v>414.0</v>
+        <v>451.0</v>
       </c>
       <c r="P187" s="2">
-        <v>265.0</v>
+        <v>300.0</v>
       </c>
       <c r="Q187" s="2">
         <v>0.0</v>
@@ -13662,7 +13662,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>569.0</v>
+        <v>643.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13674,13 +13674,13 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>569.0</v>
+        <v>643.0</v>
       </c>
       <c r="O188" s="2">
-        <v>174.0</v>
+        <v>237.0</v>
       </c>
       <c r="P188" s="2">
-        <v>337.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q188" s="2">
         <v>58.0</v>
@@ -13689,7 +13689,7 @@
         <v>70.0</v>
       </c>
       <c r="S188" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="T188" s="2">
         <v>0.0</v>
@@ -13701,7 +13701,7 @@
         <v>0.0</v>
       </c>
       <c r="W188" s="2">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
@@ -13733,7 +13733,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>609.0</v>
+        <v>720.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13745,16 +13745,16 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>609.0</v>
+        <v>720.0</v>
       </c>
       <c r="O189" s="2">
-        <v>180.0</v>
+        <v>202.0</v>
       </c>
       <c r="P189" s="2">
-        <v>160.0</v>
+        <v>248.0</v>
       </c>
       <c r="Q189" s="2">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="R189" s="2">
         <v>1.0</v>
@@ -13804,7 +13804,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>865.0</v>
+        <v>912.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13816,13 +13816,13 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>865.0</v>
+        <v>912.0</v>
       </c>
       <c r="O190" s="2">
-        <v>476.0</v>
+        <v>515.0</v>
       </c>
       <c r="P190" s="2">
-        <v>368.0</v>
+        <v>376.0</v>
       </c>
       <c r="Q190" s="2">
         <v>21.0</v>
@@ -13875,7 +13875,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>689.0</v>
+        <v>735.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13887,13 +13887,13 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>689.0</v>
+        <v>735.0</v>
       </c>
       <c r="O191" s="2">
-        <v>333.0</v>
+        <v>374.0</v>
       </c>
       <c r="P191" s="2">
-        <v>323.0</v>
+        <v>328.0</v>
       </c>
       <c r="Q191" s="2">
         <v>33.0</v>
@@ -13946,7 +13946,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>333.0</v>
+        <v>358.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -13958,13 +13958,13 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>333.0</v>
+        <v>358.0</v>
       </c>
       <c r="O192" s="2">
-        <v>184.0</v>
+        <v>203.0</v>
       </c>
       <c r="P192" s="2">
-        <v>147.0</v>
+        <v>153.0</v>
       </c>
       <c r="Q192" s="2">
         <v>2.0</v>
@@ -13973,10 +13973,10 @@
         <v>7.0</v>
       </c>
       <c r="S192" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T192" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U192" s="2">
         <v>0.0</v>
@@ -13985,7 +13985,7 @@
         <v>0.0</v>
       </c>
       <c r="W192" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -14159,7 +14159,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>346.0</v>
+        <v>361.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14171,13 +14171,13 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>346.0</v>
+        <v>361.0</v>
       </c>
       <c r="O195" s="2">
-        <v>74.0</v>
+        <v>84.0</v>
       </c>
       <c r="P195" s="2">
-        <v>146.0</v>
+        <v>151.0</v>
       </c>
       <c r="Q195" s="2">
         <v>126.0</v>
@@ -14230,7 +14230,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" s="2">
-        <v>1110.0</v>
+        <v>1129.0</v>
       </c>
       <c r="K196" s="2">
         <v>1.0</v>
@@ -14242,16 +14242,16 @@
         <v>0.0</v>
       </c>
       <c r="N196" s="2">
-        <v>1110.0</v>
+        <v>1129.0</v>
       </c>
       <c r="O196" s="2">
-        <v>431.0</v>
+        <v>437.0</v>
       </c>
       <c r="P196" s="2">
-        <v>488.0</v>
+        <v>494.0</v>
       </c>
       <c r="Q196" s="2">
-        <v>191.0</v>
+        <v>198.0</v>
       </c>
       <c r="R196" s="2">
         <v>0.0</v>
@@ -14301,7 +14301,7 @@
         <v>1163.0</v>
       </c>
       <c r="J197" s="2">
-        <v>1059.0</v>
+        <v>1063.0</v>
       </c>
       <c r="K197" s="2">
         <v>1.0</v>
@@ -14313,13 +14313,13 @@
         <v>0.0</v>
       </c>
       <c r="N197" s="2">
-        <v>1059.0</v>
+        <v>1063.0</v>
       </c>
       <c r="O197" s="2">
-        <v>593.0</v>
+        <v>596.0</v>
       </c>
       <c r="P197" s="2">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q197" s="2">
         <v>118.0</v>
@@ -14443,7 +14443,7 @@
         <v>1015.0</v>
       </c>
       <c r="J199" s="2">
-        <v>736.0</v>
+        <v>855.0</v>
       </c>
       <c r="K199" s="2">
         <v>1.0</v>
@@ -14455,22 +14455,22 @@
         <v>0.0</v>
       </c>
       <c r="N199" s="2">
-        <v>736.0</v>
+        <v>855.0</v>
       </c>
       <c r="O199" s="2">
-        <v>320.0</v>
+        <v>411.0</v>
       </c>
       <c r="P199" s="2">
-        <v>416.0</v>
+        <v>444.0</v>
       </c>
       <c r="Q199" s="2">
         <v>0.0</v>
       </c>
       <c r="R199" s="2">
-        <v>52.0</v>
+        <v>61.0</v>
       </c>
       <c r="S199" s="2">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="T199" s="2">
         <v>0.0</v>
@@ -14482,7 +14482,7 @@
         <v>1.0</v>
       </c>
       <c r="W199" s="2">
-        <v>53.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
@@ -14514,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>486.0</v>
+        <v>493.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14526,13 +14526,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>486.0</v>
+        <v>493.0</v>
       </c>
       <c r="O200" s="2">
-        <v>299.0</v>
+        <v>304.0</v>
       </c>
       <c r="P200" s="2">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
@@ -14541,10 +14541,10 @@
         <v>21.0</v>
       </c>
       <c r="S200" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T200" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U200" s="2">
         <v>0.0</v>
@@ -14553,7 +14553,7 @@
         <v>0.0</v>
       </c>
       <c r="W200" s="2">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
@@ -14585,7 +14585,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>752.0</v>
+        <v>824.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14597,34 +14597,34 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>752.0</v>
+        <v>824.0</v>
       </c>
       <c r="O201" s="2">
-        <v>390.0</v>
+        <v>433.0</v>
       </c>
       <c r="P201" s="2">
-        <v>352.0</v>
+        <v>380.0</v>
       </c>
       <c r="Q201" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R201" s="2">
         <v>23.0</v>
       </c>
       <c r="S201" s="2">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="T201" s="2">
         <v>4.0</v>
       </c>
       <c r="U201" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="V201" s="2">
         <v>1.0</v>
       </c>
       <c r="W201" s="2">
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
@@ -14656,7 +14656,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>434.0</v>
+        <v>576.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14668,13 +14668,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>434.0</v>
+        <v>576.0</v>
       </c>
       <c r="O202" s="2">
-        <v>240.0</v>
+        <v>327.0</v>
       </c>
       <c r="P202" s="2">
-        <v>194.0</v>
+        <v>249.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14727,7 +14727,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>641.0</v>
+        <v>713.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -14739,19 +14739,19 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>641.0</v>
+        <v>713.0</v>
       </c>
       <c r="O203" s="2">
-        <v>361.0</v>
+        <v>404.0</v>
       </c>
       <c r="P203" s="2">
-        <v>280.0</v>
+        <v>309.0</v>
       </c>
       <c r="Q203" s="2">
         <v>0.0</v>
       </c>
       <c r="R203" s="2">
-        <v>0.0</v>
+        <v>43.0</v>
       </c>
       <c r="S203" s="2">
         <v>0.0</v>
@@ -14766,7 +14766,7 @@
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>0.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -14798,7 +14798,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>456.0</v>
+        <v>642.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14810,13 +14810,13 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>456.0</v>
+        <v>642.0</v>
       </c>
       <c r="O204" s="2">
-        <v>244.0</v>
+        <v>353.0</v>
       </c>
       <c r="P204" s="2">
-        <v>206.0</v>
+        <v>283.0</v>
       </c>
       <c r="Q204" s="2">
         <v>6.0</v>
@@ -14831,13 +14831,13 @@
         <v>0.0</v>
       </c>
       <c r="U204" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V204" s="2">
         <v>0.0</v>
       </c>
       <c r="W204" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
@@ -14869,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>389.0</v>
+        <v>486.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14881,16 +14881,16 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>389.0</v>
+        <v>486.0</v>
       </c>
       <c r="O205" s="2">
-        <v>179.0</v>
+        <v>235.0</v>
       </c>
       <c r="P205" s="2">
-        <v>179.0</v>
+        <v>217.0</v>
       </c>
       <c r="Q205" s="2">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="R205" s="2">
         <v>0.0</v>
@@ -15011,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>447.0</v>
+        <v>490.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15023,13 +15023,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>447.0</v>
+        <v>490.0</v>
       </c>
       <c r="O207" s="2">
-        <v>253.0</v>
+        <v>282.0</v>
       </c>
       <c r="P207" s="2">
-        <v>190.0</v>
+        <v>204.0</v>
       </c>
       <c r="Q207" s="2">
         <v>4.0</v>
@@ -15082,7 +15082,7 @@
         <v>762.0</v>
       </c>
       <c r="J208" s="2">
-        <v>495.0</v>
+        <v>510.0</v>
       </c>
       <c r="K208" s="2">
         <v>1.0</v>
@@ -15094,13 +15094,13 @@
         <v>0.0</v>
       </c>
       <c r="N208" s="2">
-        <v>495.0</v>
+        <v>510.0</v>
       </c>
       <c r="O208" s="2">
-        <v>123.0</v>
+        <v>132.0</v>
       </c>
       <c r="P208" s="2">
-        <v>216.0</v>
+        <v>222.0</v>
       </c>
       <c r="Q208" s="2">
         <v>156.0</v>
@@ -15153,7 +15153,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>784.0</v>
+        <v>827.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15165,13 +15165,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>784.0</v>
+        <v>827.0</v>
       </c>
       <c r="O209" s="2">
-        <v>396.0</v>
+        <v>432.0</v>
       </c>
       <c r="P209" s="2">
-        <v>388.0</v>
+        <v>395.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
@@ -15180,10 +15180,10 @@
         <v>44.0</v>
       </c>
       <c r="S209" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="T209" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U209" s="2">
         <v>0.0</v>
@@ -15192,7 +15192,7 @@
         <v>0.0</v>
       </c>
       <c r="W209" s="2">
-        <v>44.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
@@ -15224,7 +15224,7 @@
         <v>792.0</v>
       </c>
       <c r="J210" s="2">
-        <v>606.0</v>
+        <v>643.0</v>
       </c>
       <c r="K210" s="2">
         <v>1.0</v>
@@ -15236,13 +15236,13 @@
         <v>0.0</v>
       </c>
       <c r="N210" s="2">
-        <v>606.0</v>
+        <v>643.0</v>
       </c>
       <c r="O210" s="2">
-        <v>305.0</v>
+        <v>333.0</v>
       </c>
       <c r="P210" s="2">
-        <v>301.0</v>
+        <v>310.0</v>
       </c>
       <c r="Q210" s="2">
         <v>0.0</v>
@@ -15251,10 +15251,10 @@
         <v>72.0</v>
       </c>
       <c r="S210" s="2">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="T210" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U210" s="2">
         <v>3.0</v>
@@ -15263,7 +15263,7 @@
         <v>0.0</v>
       </c>
       <c r="W210" s="2">
-        <v>146.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="211" ht="15.75" customHeight="1">
@@ -15295,7 +15295,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" s="2">
-        <v>810.0</v>
+        <v>820.0</v>
       </c>
       <c r="K211" s="2">
         <v>1.0</v>
@@ -15307,13 +15307,13 @@
         <v>0.0</v>
       </c>
       <c r="N211" s="2">
-        <v>810.0</v>
+        <v>820.0</v>
       </c>
       <c r="O211" s="2">
-        <v>415.0</v>
+        <v>419.0</v>
       </c>
       <c r="P211" s="2">
-        <v>395.0</v>
+        <v>401.0</v>
       </c>
       <c r="Q211" s="2">
         <v>0.0</v>
@@ -15366,7 +15366,7 @@
         <v>1055.0</v>
       </c>
       <c r="J212" s="2">
-        <v>688.0</v>
+        <v>739.0</v>
       </c>
       <c r="K212" s="2">
         <v>1.0</v>
@@ -15378,13 +15378,13 @@
         <v>1.0</v>
       </c>
       <c r="N212" s="2">
-        <v>687.0</v>
+        <v>738.0</v>
       </c>
       <c r="O212" s="2">
-        <v>148.0</v>
+        <v>175.0</v>
       </c>
       <c r="P212" s="2">
-        <v>320.0</v>
+        <v>344.0</v>
       </c>
       <c r="Q212" s="2">
         <v>220.0</v>
@@ -15437,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>599.0</v>
+        <v>660.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15449,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>599.0</v>
+        <v>660.0</v>
       </c>
       <c r="O213" s="2">
-        <v>307.0</v>
+        <v>338.0</v>
       </c>
       <c r="P213" s="2">
-        <v>292.0</v>
+        <v>322.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15508,7 +15508,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>522.0</v>
+        <v>540.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -15520,22 +15520,22 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>522.0</v>
+        <v>540.0</v>
       </c>
       <c r="O214" s="2">
-        <v>274.0</v>
+        <v>286.0</v>
       </c>
       <c r="P214" s="2">
-        <v>248.0</v>
+        <v>254.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
       </c>
       <c r="R214" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="S214" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T214" s="2">
         <v>0.0</v>
@@ -15547,7 +15547,7 @@
         <v>0.0</v>
       </c>
       <c r="W214" s="2">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
@@ -15579,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>689.0</v>
+        <v>720.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15591,13 +15591,13 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>689.0</v>
+        <v>720.0</v>
       </c>
       <c r="O215" s="2">
-        <v>278.0</v>
+        <v>304.0</v>
       </c>
       <c r="P215" s="2">
-        <v>411.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q215" s="2">
         <v>0.0</v>
@@ -15650,7 +15650,7 @@
         <v>576.0</v>
       </c>
       <c r="J216" s="2">
-        <v>338.0</v>
+        <v>430.0</v>
       </c>
       <c r="K216" s="2">
         <v>1.0</v>
@@ -15662,13 +15662,13 @@
         <v>0.0</v>
       </c>
       <c r="N216" s="2">
-        <v>338.0</v>
+        <v>430.0</v>
       </c>
       <c r="O216" s="2">
-        <v>171.0</v>
+        <v>233.0</v>
       </c>
       <c r="P216" s="2">
-        <v>153.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q216" s="2">
         <v>14.0</v>
@@ -15721,7 +15721,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>611.0</v>
+        <v>612.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15733,10 +15733,10 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>611.0</v>
+        <v>612.0</v>
       </c>
       <c r="O217" s="2">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="P217" s="2">
         <v>339.0</v>
@@ -15792,7 +15792,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>565.0</v>
+        <v>659.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15804,25 +15804,25 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>564.0</v>
+        <v>658.0</v>
       </c>
       <c r="O218" s="2">
-        <v>298.0</v>
+        <v>336.0</v>
       </c>
       <c r="P218" s="2">
-        <v>267.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
       </c>
       <c r="R218" s="2">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
       <c r="S218" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T218" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U218" s="2">
         <v>0.0</v>
@@ -15831,7 +15831,7 @@
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>20.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15863,7 +15863,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>829.0</v>
+        <v>856.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15875,13 +15875,13 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>829.0</v>
+        <v>856.0</v>
       </c>
       <c r="O219" s="2">
-        <v>102.0</v>
+        <v>115.0</v>
       </c>
       <c r="P219" s="2">
-        <v>355.0</v>
+        <v>369.0</v>
       </c>
       <c r="Q219" s="2">
         <v>372.0</v>
@@ -15890,10 +15890,10 @@
         <v>22.0</v>
       </c>
       <c r="S219" s="2">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="T219" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U219" s="2">
         <v>1.0</v>
@@ -15902,7 +15902,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -16147,7 +16147,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>711.0</v>
+        <v>768.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16159,19 +16159,19 @@
         <v>0.0</v>
       </c>
       <c r="N223" s="2">
-        <v>711.0</v>
+        <v>768.0</v>
       </c>
       <c r="O223" s="2">
-        <v>66.0</v>
+        <v>94.0</v>
       </c>
       <c r="P223" s="2">
-        <v>245.0</v>
+        <v>263.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>400.0</v>
+        <v>411.0</v>
       </c>
       <c r="R223" s="2">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="S223" s="2">
         <v>0.0</v>
@@ -16186,7 +16186,7 @@
         <v>0.0</v>
       </c>
       <c r="W223" s="2">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -16218,7 +16218,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>438.0</v>
+        <v>486.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16230,16 +16230,16 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>438.0</v>
+        <v>486.0</v>
       </c>
       <c r="O224" s="2">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="P224" s="2">
-        <v>33.0</v>
+        <v>38.0</v>
       </c>
       <c r="Q224" s="2">
-        <v>386.0</v>
+        <v>427.0</v>
       </c>
       <c r="R224" s="2">
         <v>1.0</v>
@@ -16289,7 +16289,7 @@
         <v>1423.0</v>
       </c>
       <c r="J225" s="2">
-        <v>1263.0</v>
+        <v>1266.0</v>
       </c>
       <c r="K225" s="2">
         <v>1.0</v>
@@ -16301,34 +16301,34 @@
         <v>0.0</v>
       </c>
       <c r="N225" s="2">
-        <v>1263.0</v>
+        <v>1266.0</v>
       </c>
       <c r="O225" s="2">
         <v>720.0</v>
       </c>
       <c r="P225" s="2">
-        <v>543.0</v>
+        <v>545.0</v>
       </c>
       <c r="Q225" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R225" s="2">
-        <v>9.0</v>
+        <v>45.0</v>
       </c>
       <c r="S225" s="2">
-        <v>20.0</v>
+        <v>73.0</v>
       </c>
       <c r="T225" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="U225" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V225" s="2">
         <v>0.0</v>
       </c>
       <c r="W225" s="2">
-        <v>29.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
@@ -16360,7 +16360,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>685.0</v>
+        <v>746.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16372,19 +16372,19 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>685.0</v>
+        <v>746.0</v>
       </c>
       <c r="O226" s="2">
-        <v>46.0</v>
+        <v>81.0</v>
       </c>
       <c r="P226" s="2">
-        <v>318.0</v>
+        <v>342.0</v>
       </c>
       <c r="Q226" s="2">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="R226" s="2">
-        <v>120.0</v>
+        <v>123.0</v>
       </c>
       <c r="S226" s="2">
         <v>21.0</v>
@@ -16399,7 +16399,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" s="2">
-        <v>141.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -16431,7 +16431,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" s="2">
-        <v>214.0</v>
+        <v>244.0</v>
       </c>
       <c r="K227" s="2">
         <v>1.0</v>
@@ -16443,22 +16443,22 @@
         <v>0.0</v>
       </c>
       <c r="N227" s="2">
-        <v>214.0</v>
+        <v>244.0</v>
       </c>
       <c r="O227" s="2">
-        <v>122.0</v>
+        <v>145.0</v>
       </c>
       <c r="P227" s="2">
-        <v>92.0</v>
+        <v>99.0</v>
       </c>
       <c r="Q227" s="2">
         <v>0.0</v>
       </c>
       <c r="R227" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="S227" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T227" s="2">
         <v>0.0</v>
@@ -16470,7 +16470,7 @@
         <v>0.0</v>
       </c>
       <c r="W227" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
@@ -16502,7 +16502,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>629.0</v>
+        <v>830.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16514,16 +16514,16 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>629.0</v>
+        <v>830.0</v>
       </c>
       <c r="O228" s="2">
-        <v>52.0</v>
+        <v>178.0</v>
       </c>
       <c r="P228" s="2">
-        <v>264.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q228" s="2">
-        <v>313.0</v>
+        <v>323.0</v>
       </c>
       <c r="R228" s="2">
         <v>0.0</v>
@@ -16597,7 +16597,7 @@
         <v>0.0</v>
       </c>
       <c r="R229" s="2">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="S229" s="2">
         <v>0.0</v>
@@ -16612,7 +16612,7 @@
         <v>0.0</v>
       </c>
       <c r="W229" s="2">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
@@ -16644,7 +16644,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>499.0</v>
+        <v>555.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16656,16 +16656,16 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>499.0</v>
+        <v>555.0</v>
       </c>
       <c r="O230" s="2">
-        <v>83.0</v>
+        <v>112.0</v>
       </c>
       <c r="P230" s="2">
-        <v>226.0</v>
+        <v>251.0</v>
       </c>
       <c r="Q230" s="2">
-        <v>190.0</v>
+        <v>192.0</v>
       </c>
       <c r="R230" s="2">
         <v>0.0</v>
@@ -16715,7 +16715,7 @@
         <v>1070.0</v>
       </c>
       <c r="J231" s="2">
-        <v>660.0</v>
+        <v>762.0</v>
       </c>
       <c r="K231" s="2">
         <v>1.0</v>
@@ -16727,22 +16727,22 @@
         <v>0.0</v>
       </c>
       <c r="N231" s="2">
-        <v>660.0</v>
+        <v>762.0</v>
       </c>
       <c r="O231" s="2">
-        <v>340.0</v>
+        <v>396.0</v>
       </c>
       <c r="P231" s="2">
-        <v>299.0</v>
+        <v>345.0</v>
       </c>
       <c r="Q231" s="2">
         <v>21.0</v>
       </c>
       <c r="R231" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="S231" s="2">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
       <c r="T231" s="2">
         <v>1.0</v>
@@ -16754,7 +16754,7 @@
         <v>0.0</v>
       </c>
       <c r="W231" s="2">
-        <v>70.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -16786,7 +16786,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>607.0</v>
+        <v>697.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16798,16 +16798,16 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>607.0</v>
+        <v>697.0</v>
       </c>
       <c r="O232" s="2">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="P232" s="2">
-        <v>118.0</v>
+        <v>128.0</v>
       </c>
       <c r="Q232" s="2">
-        <v>484.0</v>
+        <v>549.0</v>
       </c>
       <c r="R232" s="2">
         <v>1.0</v>
@@ -16857,7 +16857,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" s="2">
-        <v>438.0</v>
+        <v>463.0</v>
       </c>
       <c r="K233" s="2">
         <v>1.0</v>
@@ -16869,13 +16869,13 @@
         <v>0.0</v>
       </c>
       <c r="N233" s="2">
-        <v>438.0</v>
+        <v>463.0</v>
       </c>
       <c r="O233" s="2">
-        <v>82.0</v>
+        <v>93.0</v>
       </c>
       <c r="P233" s="2">
-        <v>215.0</v>
+        <v>229.0</v>
       </c>
       <c r="Q233" s="2">
         <v>141.0</v>
@@ -16884,7 +16884,7 @@
         <v>3.0</v>
       </c>
       <c r="S233" s="2">
-        <v>7.0</v>
+        <v>19.0</v>
       </c>
       <c r="T233" s="2">
         <v>0.0</v>
@@ -16896,7 +16896,7 @@
         <v>0.0</v>
       </c>
       <c r="W233" s="2">
-        <v>10.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="234" ht="15.75" customHeight="1"/>
